--- a/output/test_cases/MART_SmartSearch_Combined_TestCases_v3.0_20260818_EN.xlsx
+++ b/output/test_cases/MART_SmartSearch_Combined_TestCases_v3.0_20260818_EN.xlsx
@@ -107,7 +107,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -136,6 +136,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2E5E4E"/>
         <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,7 +179,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -276,6 +282,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -900,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="16" min="1" max="1"/>
@@ -2927,7 +2936,7 @@
       </c>
       <c r="L33" s="26" t="inlineStr">
         <is>
-          <t>QnA-04</t>
+          <t>QnA-35</t>
         </is>
       </c>
       <c r="M33" s="28" t="n"/>
@@ -2935,7 +2944,7 @@
       <c r="O33" s="28" t="n"/>
       <c r="P33" s="26" t="inlineStr">
         <is>
-          <t>OPEN — QnA-04: xem chi tiết trong file QnA log.</t>
+          <t>OPEN — QnA-35: xem chi tiết trong file QnA log.</t>
         </is>
       </c>
     </row>
@@ -5238,6 +5247,954 @@
       <c r="N70" s="28" t="n"/>
       <c r="O70" s="28" t="n"/>
       <c r="P70" s="27" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC7</t>
+        </is>
+      </c>
+      <c r="C71" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D71" s="27" t="inlineStr">
+        <is>
+          <t>E. Search Results — Grid</t>
+        </is>
+      </c>
+      <c r="E71" s="27" t="inlineStr">
+        <is>
+          <t>FR-PR-06</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G71" s="27" t="inlineStr">
+        <is>
+          <t>Check the default sort criterion on first entry to the results page (before the user has ever changed Sort).</t>
+        </is>
+      </c>
+      <c r="H71" s="27" t="inlineStr">
+        <is>
+          <t>"milk" (first search in the session)</t>
+        </is>
+      </c>
+      <c r="I71" s="27" t="inlineStr">
+        <is>
+          <t>The customer has never selected a Sort option in the current session/device.</t>
+        </is>
+      </c>
+      <c r="J71" s="27" t="inlineStr">
+        <is>
+          <t>The results page defaults to "Most Relevant" (AI Scorecard Ranking); the label on the sticky Sort bar correctly shows "Most Relevant" from the very first load, with no action required from the customer.</t>
+        </is>
+      </c>
+      <c r="K71" s="27" t="inlineStr">
+        <is>
+          <t>The default sort is always "Most Relevant" per FR-PR-06, matching the initial state described in SS-SCR-008-SC2.</t>
+        </is>
+      </c>
+      <c r="L71" s="27" t="n"/>
+      <c r="M71" s="28" t="n"/>
+      <c r="N71" s="28" t="n"/>
+      <c r="O71" s="28" t="n"/>
+      <c r="P71" s="27" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC8</t>
+        </is>
+      </c>
+      <c r="C72" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D72" s="27" t="inlineStr">
+        <is>
+          <t>E. Search Results — Grid</t>
+        </is>
+      </c>
+      <c r="E72" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G72" s="27" t="inlineStr">
+        <is>
+          <t>Check the default state of the "Filter" button when no filter condition has been applied yet.</t>
+        </is>
+      </c>
+      <c r="H72" s="27" t="inlineStr">
+        <is>
+          <t>"milk" (no filter applied)</t>
+        </is>
+      </c>
+      <c r="I72" s="27" t="inlineStr">
+        <is>
+          <t>The results page has just loaded; the customer has never opened/applied the detailed Filter sheet.</t>
+        </is>
+      </c>
+      <c r="J72" s="27" t="inlineStr">
+        <is>
+          <t>The "Filter" button shows its default state with no count badge (or a badge=0 that is fully hidden); no filter chip is active on the results page; the total result count is the full, unfiltered set.</t>
+        </is>
+      </c>
+      <c r="K72" s="27" t="inlineStr">
+        <is>
+          <t>The badge only appears once &gt;=1 filter condition is applied — consistent with the behavior described in SS-SCR-010-SC3 (badge=0 returns to default).</t>
+        </is>
+      </c>
+      <c r="L72" s="27" t="n"/>
+      <c r="M72" s="28" t="n"/>
+      <c r="N72" s="28" t="n"/>
+      <c r="O72" s="28" t="n"/>
+      <c r="P72" s="27" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9</t>
+        </is>
+      </c>
+      <c r="C73" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D73" s="27" t="inlineStr">
+        <is>
+          <t>E. Search Results — Grid</t>
+        </is>
+      </c>
+      <c r="E73" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-02, FR-SF-03</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="G73" s="27" t="inlineStr">
+        <is>
+          <t>Interact directly with the Smart Filter Chips right on the results page (without opening the detailed Filter sheet).</t>
+        </is>
+      </c>
+      <c r="H73" s="27" t="inlineStr">
+        <is>
+          <t>Tap 1 chip (e.g. "Organic") then tap a second chip (e.g. "Sugar-free")</t>
+        </is>
+      </c>
+      <c r="I73" s="27" t="inlineStr">
+        <is>
+          <t>The results page has loaded, and the Smart Filter Chips row is shown for the current keyword (up to 10 chips, flat structure — not grouped).</t>
+        </is>
+      </c>
+      <c r="J73" s="27" t="inlineStr">
+        <is>
+          <t>Tapping 1 chip applies the filter immediately (no separate "Apply" button needed); the chip switches to an active state; results update in real time; the "Filter" button badge increments accordingly. Tapping a second chip applies both conditions combined (AND). Every chip shown must always resolve to &gt;=1 product, per FR-SF-01-&gt;03.</t>
+        </is>
+      </c>
+      <c r="K73" s="27" t="inlineStr">
+        <is>
+          <t>No chip shown ever resolves to 0 results when tapped; the badge stays in sync between the Smart Filter Chips and the detailed Filter sheet (SS-SCR-009), since they share the same filter state.</t>
+        </is>
+      </c>
+      <c r="L73" s="27" t="n"/>
+      <c r="M73" s="28" t="n"/>
+      <c r="N73" s="28" t="n"/>
+      <c r="O73" s="28" t="n"/>
+      <c r="P73" s="27" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC4</t>
+        </is>
+      </c>
+      <c r="C74" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D74" s="27" t="inlineStr">
+        <is>
+          <t>F. Search Results — List</t>
+        </is>
+      </c>
+      <c r="E74" s="27" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-07</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G74" s="27" t="inlineStr">
+        <is>
+          <t>Tap a Product Card (outside the + button) in List view to open the PDP.</t>
+        </is>
+      </c>
+      <c r="H74" s="27" t="inlineStr">
+        <is>
+          <t>Any 1 product row in List view</t>
+        </is>
+      </c>
+      <c r="I74" s="27" t="inlineStr">
+        <is>
+          <t>View mode = List, results page has loaded.</t>
+        </is>
+      </c>
+      <c r="J74" s="27" t="inlineStr">
+        <is>
+          <t>Tapping the image/name/price area of the product row (outside the + button) opens the correct PDP for that product, matching the equivalent Grid-view behavior (SS-SCR-005-SC3-TC1); does not accidentally trigger add-to-cart.</t>
+        </is>
+      </c>
+      <c r="K74" s="27" t="inlineStr">
+        <is>
+          <t>Opening the PDP is consistent between the Grid and List view modes.</t>
+        </is>
+      </c>
+      <c r="L74" s="27" t="n"/>
+      <c r="M74" s="28" t="n"/>
+      <c r="N74" s="28" t="n"/>
+      <c r="O74" s="28" t="n"/>
+      <c r="P74" s="27" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="35" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC5</t>
+        </is>
+      </c>
+      <c r="C75" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D75" s="35" t="inlineStr">
+        <is>
+          <t>F. Search Results — List</t>
+        </is>
+      </c>
+      <c r="E75" s="35" t="inlineStr">
+        <is>
+          <t>No clear FR ID in the BRD — see QnA-10</t>
+        </is>
+      </c>
+      <c r="F75" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G75" s="35" t="inlineStr">
+        <is>
+          <t>Tap the (+) quick-add button on a product row in List view.</t>
+        </is>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>Tap (+) on 1 in-stock product row in List view</t>
+        </is>
+      </c>
+      <c r="I75" s="35" t="inlineStr">
+        <is>
+          <t>View mode = List, results page has loaded.</t>
+        </is>
+      </c>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>The cart badge increments immediately (optimistic update); a confirmation Toast appears at the bottom of the screen, matching the Grid-view behavior (SS-SCR-011); stays on the results page, does not accidentally open the PDP.</t>
+        </is>
+      </c>
+      <c r="K75" s="35" t="inlineStr">
+        <is>
+          <t>Add-to-cart behavior is consistent between Grid and List view modes; the (+) tap target and the PDP tap target do not overlap in the List row layout.</t>
+        </is>
+      </c>
+      <c r="L75" s="35" t="inlineStr">
+        <is>
+          <t>QnA-10</t>
+        </is>
+      </c>
+      <c r="M75" s="28" t="n"/>
+      <c r="N75" s="28" t="n"/>
+      <c r="O75" s="28" t="n"/>
+      <c r="P75" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-10: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="35" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6</t>
+        </is>
+      </c>
+      <c r="C76" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D76" s="35" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E76" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F76" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G76" s="35" t="inlineStr">
+        <is>
+          <t>Check the mechanism for counting selected conditions — a per-tab badge inside the Filter sheet, and a total badge on the "Filter" button on the results page.</t>
+        </is>
+      </c>
+      <c r="H76" s="35" t="inlineStr">
+        <is>
+          <t>Select 1 Category + 3 Label chips + 1 Rating level + 1 Delivery condition + 1 Price range</t>
+        </is>
+      </c>
+      <c r="I76" s="35" t="inlineStr">
+        <is>
+          <t>The results page has loaded; no filter condition has been applied yet.</t>
+        </is>
+      </c>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>Per the real Figma reference (Text Search.png): each tab on the left (Category/Labels/Delivery/Rating/Price) shows its own count badge = the number of conditions SELECTED WITHIN THAT TAB (e.g. Labels with 3 chips selected -&gt; Labels tab badge = "3"); the "Apply" button at the bottom of the sheet does NOT carry a "(n)" count suffix (just plain "Apply"). TBD: whether the "Filter" button on the results page (outside the sheet) shows a total badge — see QnA-39.</t>
+        </is>
+      </c>
+      <c r="K76" s="35" t="inlineStr">
+        <is>
+          <t>Each per-tab badge must exactly match the number of conditions active in that tab at all times (even before tapping Apply).</t>
+        </is>
+      </c>
+      <c r="L76" s="35" t="inlineStr">
+        <is>
+          <t>QnA-39</t>
+        </is>
+      </c>
+      <c r="M76" s="28" t="n"/>
+      <c r="N76" s="28" t="n"/>
+      <c r="O76" s="28" t="n"/>
+      <c r="P76" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-39: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="27" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7</t>
+        </is>
+      </c>
+      <c r="C77" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D77" s="27" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E77" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G77" s="27" t="inlineStr">
+        <is>
+          <t>Check the detailed behavior of the "Reset" button and the "Apply" button on the sheet's fixed bottom action bar.</t>
+        </is>
+      </c>
+      <c r="H77" s="27" t="inlineStr">
+        <is>
+          <t>Tap "Reset" after selecting several conditions; tap "Apply" in different states</t>
+        </is>
+      </c>
+      <c r="I77" s="27" t="inlineStr">
+        <is>
+          <t>The Filter sheet is open with the fixed "Reset"/"Apply" action bar shown (per the real Figma reference, see QnA-18).</t>
+        </is>
+      </c>
+      <c r="J77" s="27" t="inlineStr">
+        <is>
+          <t>"Reset" clears every selection currently IN THE SHEET (not yet applied) back to empty, but the sheet stays open (does not auto-close); "Apply" always closes the sheet and re-runs the query based on the sheet's exact state at the moment of the tap, even if that state is empty (0 conditions) or unchanged from before.</t>
+        </is>
+      </c>
+      <c r="K77" s="27" t="inlineStr">
+        <is>
+          <t>The two buttons behave independently and are not to be confused with the (X) close button (which does not apply changes and restores the previous state), already tested in SC5.</t>
+        </is>
+      </c>
+      <c r="L77" s="27" t="n"/>
+      <c r="M77" s="28" t="n"/>
+      <c r="N77" s="28" t="n"/>
+      <c r="O77" s="28" t="n"/>
+      <c r="P77" s="27" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="27" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8</t>
+        </is>
+      </c>
+      <c r="C78" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G78" s="27" t="inlineStr">
+        <is>
+          <t>Switch back and forth between the condition-group tabs (Category/Labels/Delivery/Rating/Price) in the Filter sheet.</t>
+        </is>
+      </c>
+      <c r="H78" s="27" t="inlineStr">
+        <is>
+          <t>Tap each left-side tab in turn; select a condition in one tab, switch to another tab, then switch back</t>
+        </is>
+      </c>
+      <c r="I78" s="27" t="inlineStr">
+        <is>
+          <t>The Filter sheet is open, the "Category" tab is active by default.</t>
+        </is>
+      </c>
+      <c r="J78" s="27" t="inlineStr">
+        <is>
+          <t>Tapping any tab immediately swaps the right-hand panel to that tab's condition group; the tapped tab is marked active (red left border + bold red text, per the real Figma reference); the other tabs return to an inactive state; selections already made in other tabs (if any) are not lost when switching back and forth, and each tab's own badge is preserved.</t>
+        </is>
+      </c>
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>Switching tabs never loses a selection made in another tab; exactly 1 tab is active at a time; the panel content always matches the currently active tab.</t>
+        </is>
+      </c>
+      <c r="L78" s="27" t="n"/>
+      <c r="M78" s="28" t="n"/>
+      <c r="N78" s="28" t="n"/>
+      <c r="O78" s="28" t="n"/>
+      <c r="P78" s="27" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="35" t="n">
+        <v>79</v>
+      </c>
+      <c r="B79" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC9</t>
+        </is>
+      </c>
+      <c r="C79" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D79" s="35" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E79" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F79" s="35" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="G79" s="35" t="inlineStr">
+        <is>
+          <t>Select a Delivery condition in the "Delivery" tab.</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>Select "Standard delivery"</t>
+        </is>
+      </c>
+      <c r="I79" s="35" t="inlineStr">
+        <is>
+          <t>The results page has loaded; no Delivery condition has been applied yet.</t>
+        </is>
+      </c>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>The updated storyboard (v0.1-20260819) confirms the Delivery tab has exactly 1 checkbox, "Standard delivery" (a simple on/off toggle), with no other delivery type in v1. Selecting the checkbox filters to SKUs eligible for standard delivery; deselecting it returns to no filtering on this condition. See QnA-42 (now Resolved).</t>
+        </is>
+      </c>
+      <c r="K79" s="35" t="inlineStr">
+        <is>
+          <t>Selecting/deselecting the Delivery condition correctly updates the Delivery tab badge and the corresponding filtered results.</t>
+        </is>
+      </c>
+      <c r="L79" s="35" t="inlineStr">
+        <is>
+          <t>QnA-42</t>
+        </is>
+      </c>
+      <c r="M79" s="28" t="n"/>
+      <c r="N79" s="28" t="n"/>
+      <c r="O79" s="28" t="n"/>
+      <c r="P79" s="35" t="inlineStr">
+        <is>
+          <t>RESOLVED — QnA-42: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10</t>
+        </is>
+      </c>
+      <c r="C80" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F80" s="27" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="G80" s="27" t="inlineStr">
+        <is>
+          <t>Select a Rating level in the "Rating" tab — 5 levels, single-select only.</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
+        <is>
+          <t>Select "5 stars", "4 stars &amp; up", ... in turn</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>The results page has loaded; no Rating condition has been applied yet.</t>
+        </is>
+      </c>
+      <c r="J80" s="27" t="inlineStr">
+        <is>
+          <t>The tab correctly shows the 5 levels per the BRD (5 stars / 4 stars &amp; up / 3 stars &amp; up / 2 stars &amp; up / 1 star &amp; up); only 1 level can be selected at a time (single-select, like Category); selecting "N stars &amp; up" returns SKUs with rating &gt;= N (including N and above, not exactly N only).</t>
+        </is>
+      </c>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Changing the Rating level automatically deselects the previous one; results correctly reflect the &gt;= N stars threshold for each level.</t>
+        </is>
+      </c>
+      <c r="L80" s="27" t="n"/>
+      <c r="M80" s="28" t="n"/>
+      <c r="N80" s="28" t="n"/>
+      <c r="O80" s="28" t="n"/>
+      <c r="P80" s="27" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="35" t="n">
+        <v>50</v>
+      </c>
+      <c r="B81" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4</t>
+        </is>
+      </c>
+      <c r="C81" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D81" s="35" t="inlineStr">
+        <is>
+          <t>K. Zero-Result Recovery</t>
+        </is>
+      </c>
+      <c r="E81" s="35" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07, FR-PR-01 -&gt; FR-PR-05 (Out-of-stock override)</t>
+        </is>
+      </c>
+      <c r="F81" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G81" s="35" t="inlineStr">
+        <is>
+          <t>Check the trigger boundary for the Zero Result Page when a keyword exactly matches 1 or more SKUs that are out of stock.</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>Keyword exactly matches an out-of-stock SKU (with other in-stock SKUs also matching) / a keyword where ALL matching SKUs are out of stock</t>
+        </is>
+      </c>
+      <c r="I81" s="35" t="inlineStr">
+        <is>
+          <t>The catalogue has SKUs that directly match the keyword but are out of stock (stock=0).</t>
+        </is>
+      </c>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>When other matching SKUs are still in stock: the system stays on SS-SCR-005 as normal, the out-of-stock SKU is pushed to the bottom of the list per the Out-of-stock override rule (FR-PR-01-&gt;05), the Zero Result Page is NOT triggered. When ALL matching SKUs are out of stock: TBD — see QnA-44.</t>
+        </is>
+      </c>
+      <c r="K81" s="35" t="inlineStr">
+        <is>
+          <t>The "You might like" block (unique to SS-SCR-012) should only ever appear when the flow genuinely falls into Zero Result — never appearing on SS-SCR-005 while a direct keyword match still exists (even if out of stock).</t>
+        </is>
+      </c>
+      <c r="L81" s="35" t="inlineStr">
+        <is>
+          <t>QnA-44</t>
+        </is>
+      </c>
+      <c r="M81" s="28" t="n"/>
+      <c r="N81" s="28" t="n"/>
+      <c r="O81" s="28" t="n"/>
+      <c r="P81" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-44: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="35" t="n">
+        <v>51</v>
+      </c>
+      <c r="B82" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-010-SC4</t>
+        </is>
+      </c>
+      <c r="C82" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-010</t>
+        </is>
+      </c>
+      <c r="D82" s="35" t="inlineStr">
+        <is>
+          <t>I. Filter Applied State</t>
+        </is>
+      </c>
+      <c r="E82" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-03</t>
+        </is>
+      </c>
+      <c r="F82" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G82" s="35" t="inlineStr">
+        <is>
+          <t>Check that the applied filter automatically clears when the customer searches a brand-new keyword (not editing the existing keyword, but searching a different one entirely).</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>Filtering by "Sugar-free" for keyword "milk" -&gt; search a new keyword "beer"</t>
+        </is>
+      </c>
+      <c r="I82" s="35" t="inlineStr">
+        <is>
+          <t>The "milk" results page has &gt;=1 filter condition applied.</t>
+        </is>
+      </c>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>Per the updated storyboard (v0.1-20260819, SS-SCR-010): when the customer searches a brand-NEW keyword (a different one), the filter applied to the old keyword AUTOMATICALLY CLEARS and does not carry over to the new keyword's results. The Filter button badge resets to 0/hidden for the new keyword.</t>
+        </is>
+      </c>
+      <c r="K82" s="35" t="inlineStr">
+        <is>
+          <t>Changing keywords always restarts the filter state from scratch (badge=0); no leftover filter chip from the old keyword appears on the new keyword's results.</t>
+        </is>
+      </c>
+      <c r="L82" s="35" t="inlineStr">
+        <is>
+          <t>QnA-06</t>
+        </is>
+      </c>
+      <c r="M82" s="28" t="n"/>
+      <c r="N82" s="28" t="n"/>
+      <c r="O82" s="28" t="n"/>
+      <c r="P82" s="35" t="inlineStr">
+        <is>
+          <t>RESOLVED — QnA-06: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="35" t="n">
+        <v>56</v>
+      </c>
+      <c r="B83" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4</t>
+        </is>
+      </c>
+      <c r="C83" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D83" s="35" t="inlineStr">
+        <is>
+          <t>M. Image Search — Gallery</t>
+        </is>
+      </c>
+      <c r="E83" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="F83" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G83" s="35" t="inlineStr">
+        <is>
+          <t>Close the Gallery bottom sheet via the "X" button in the header, or by tapping the dimmed area outside the sheet.</t>
+        </is>
+      </c>
+      <c r="H83" s="35" t="inlineStr">
+        <is>
+          <t>Tap the "X" button / tap the dimmed area behind the sheet</t>
+        </is>
+      </c>
+      <c r="I83" s="35" t="inlineStr">
+        <is>
+          <t>The "Recent Photos" Gallery sheet is open, no photo selected yet.</t>
+        </is>
+      </c>
+      <c r="J83" s="35" t="inlineStr">
+        <is>
+          <t>Both dismissal methods correctly return to the Camera Screen (SS-SCR-013) with no photo selected, preserving the current camera state (front/back, flash) — matching the storyboard's description "Close tray -&gt; return to the capture screen without selecting any photo".</t>
+        </is>
+      </c>
+      <c r="K83" s="35" t="inlineStr">
+        <is>
+          <t>Both dismissal methods (X button / tap outside) produce consistent results; no photo is ever accidentally selected when dismissing.</t>
+        </is>
+      </c>
+      <c r="L83" s="35" t="n"/>
+      <c r="M83" s="28" t="n"/>
+      <c r="N83" s="28" t="n"/>
+      <c r="O83" s="28" t="n"/>
+      <c r="P83" s="35" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="35" t="n">
+        <v>69</v>
+      </c>
+      <c r="B84" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C84" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D84" s="35" t="inlineStr">
+        <is>
+          <t>P. Voice Search — Listening</t>
+        </is>
+      </c>
+      <c r="E84" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="F84" s="35" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="G84" s="35" t="inlineStr">
+        <is>
+          <t>Multilingual recognition (EN/KR/CN/RU) with automatic language detection, no manual language selection required.</t>
+        </is>
+      </c>
+      <c r="H84" s="35" t="inlineStr">
+        <is>
+          <t>Speak in English / Korean / Chinese / Russian</t>
+        </is>
+      </c>
+      <c r="I84" s="35" t="inlineStr">
+        <is>
+          <t>Mic permission is granted; the recording layer is active.</t>
+        </is>
+      </c>
+      <c r="J84" s="35" t="inlineStr">
+        <is>
+          <t>The system automatically detects the language being spoken (no manual language-selection UI) and transcribes it accurately for all 4 languages EN/KR/CN/RU, processing it exactly like a Vietnamese query (per FR-VS-01).</t>
+        </is>
+      </c>
+      <c r="K84" s="35" t="inlineStr">
+        <is>
+          <t>No language-selection step ever blocks the flow; transcription accuracy is acceptable for all 4 languages; search results return the corresponding relevant products.</t>
+        </is>
+      </c>
+      <c r="L84" s="35" t="n"/>
+      <c r="M84" s="28" t="n"/>
+      <c r="N84" s="28" t="n"/>
+      <c r="O84" s="28" t="n"/>
+      <c r="P84" s="35" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="B85" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC3</t>
+        </is>
+      </c>
+      <c r="C85" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-018</t>
+        </is>
+      </c>
+      <c r="D85" s="35" t="inlineStr">
+        <is>
+          <t>Q. Voice Search — Result</t>
+        </is>
+      </c>
+      <c r="E85" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-08, NFR-005</t>
+        </is>
+      </c>
+      <c r="F85" s="35" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="G85" s="35" t="inlineStr">
+        <is>
+          <t>Measure end-to-end voice search response time (from the end of speech to the first result displayed).</t>
+        </is>
+      </c>
+      <c r="H85" s="35" t="inlineStr">
+        <is>
+          <t>Standard speech, normal network conditions</t>
+        </is>
+      </c>
+      <c r="I85" s="35" t="inlineStr">
+        <is>
+          <t>Normal network conditions.</t>
+        </is>
+      </c>
+      <c r="J85" s="35" t="inlineStr">
+        <is>
+          <t>TBD — FR-VS-08 states a 6,000ms P95 threshold, NFR-005 states 4,000ms P95 for the same measurement — the two figures conflict (see QnA-30, open). This test case measures the actual P95 but cannot be scored Pass/Fail until BA/TD locks in one official number.</t>
+        </is>
+      </c>
+      <c r="K85" s="35" t="inlineStr">
+        <is>
+          <t>P95 must fall within the official threshold ONCE confirmed (4,000ms or 6,000ms).</t>
+        </is>
+      </c>
+      <c r="L85" s="35" t="inlineStr">
+        <is>
+          <t>QnA-30</t>
+        </is>
+      </c>
+      <c r="M85" s="28" t="n"/>
+      <c r="N85" s="28" t="n"/>
+      <c r="O85" s="28" t="n"/>
+      <c r="P85" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-30: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5255,7 +6212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q177"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="16" min="1" max="1"/>
@@ -5656,42 +6613,42 @@
       <c r="Q6" s="27" t="n"/>
     </row>
     <row r="7" ht="46.25" customHeight="1" s="17">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>SS-SCR-001-SC2-TC3</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>SS-SCR-001-SC2</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>SS-SCR-001</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>FR-SP-02, FR-IS-02, FR-VS-02, FR-PS-01, FR-PS-02, FR-PS-03, FR-PS-04</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>"Clear all" only clears the local device, not synced across devices</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>The shopper is logged in on 2 different devices (Device A and Device B), each with its own previously-cached Recent Searches history.</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>1. On Device A, build up a Recent Searches history (3-5 keywords).
 2. On Device B, log in to the same account and separately build up its own Recent Searches history.
@@ -5700,17 +6657,17 @@
 5. Log out and back in on Device B (or refresh the app) and check again.</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="I7" s="35" t="inlineStr">
         <is>
           <t>2 devices under the same Member account, each with a different local Recent Searches cache.</t>
         </is>
       </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="J7" s="35" t="inlineStr">
         <is>
           <t>TBD — "Clear all" only clears Device A's local storage. Device B's own cached Recent Searches is expected to stay unchanged right after step 3/4 (Recent Searches is client-local), unless the system has a server-side sync mechanism, which is not yet confirmed. Do not mark Pass/Fail until BA confirms — see QnA-27.</t>
         </is>
       </c>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="K7" s="35" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5723,12 +6680,12 @@
       </c>
       <c r="N7" s="28" t="n"/>
       <c r="O7" s="28" t="n"/>
-      <c r="P7" s="27" t="inlineStr">
+      <c r="P7" s="35" t="inlineStr">
         <is>
           <t>QnA-27</t>
         </is>
       </c>
-      <c r="Q7" s="27" t="inlineStr">
+      <c r="Q7" s="35" t="inlineStr">
         <is>
           <t>OPEN: cross-device Recent Searches sync behavior is not documented. Logged as QnA-27.</t>
         </is>
@@ -6087,59 +7044,59 @@
       <c r="Q12" s="27" t="n"/>
     </row>
     <row r="13" ht="79.84999999999999" customHeight="1" s="17">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>SS-SCR-001-SC4-TC1</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>SS-SCR-001-SC4</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>SS-SCR-001</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>FR-SP-02, FR-IS-02, FR-VS-02, FR-PS-01, FR-PS-02, FR-PS-03, FR-PS-04</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
-      <c r="F13" s="27" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>"Frequently Purchased" ranks by number of Orders (Order Count), not by item quantity</t>
         </is>
       </c>
-      <c r="G13" s="27" t="inlineStr">
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>OMS has order-history data. Some SKUs are out of stock (stock=0).</t>
         </is>
       </c>
-      <c r="H13" s="27" t="inlineStr">
+      <c r="H13" s="35" t="inlineStr">
         <is>
           <t>1. Log in to an account with this history: SKU-A bought in 3 separate orders (1 unit each); SKU-B bought in 1 order (5 units in that order).
 2. Go to the Pre-search screen, look at "Frequently Purchased".
 3. Compare the position of SKU-A and SKU-B.</t>
         </is>
       </c>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="I13" s="35" t="inlineStr">
         <is>
           <t>SKU-A: 3 orders x 1 unit; SKU-B: 1 order x 5 units</t>
         </is>
       </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="J13" s="35" t="inlineStr">
         <is>
           <t>SKU-A ranks above SKU-B because it counts NUMBER OF ORDERS (3 &gt; 1), not total item quantity (1x3=3 vs 5) — matches FR-PS-03: "never count by quantity inside an order".</t>
         </is>
       </c>
-      <c r="K13" s="27" t="inlineStr">
+      <c r="K13" s="35" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -6152,12 +7109,12 @@
       </c>
       <c r="N13" s="28" t="n"/>
       <c r="O13" s="28" t="n"/>
-      <c r="P13" s="27" t="inlineStr">
+      <c r="P13" s="35" t="inlineStr">
         <is>
           <t>QnA-29</t>
         </is>
       </c>
-      <c r="Q13" s="27" t="inlineStr">
+      <c r="Q13" s="35" t="inlineStr">
         <is>
           <t>Cross-referenced with QnA-29 (Storyboard vs BRD conflict on the order-history lookback window) — the conclusion that SKU-A ranks above SKU-B (counted by order count, not quantity) does not depend on the exact window length; noted here for traceability.</t>
         </is>
@@ -9417,7 +10374,7 @@
       <c r="O59" s="28" t="n"/>
       <c r="P59" s="26" t="inlineStr">
         <is>
-          <t>QnA-04</t>
+          <t>QnA-35</t>
         </is>
       </c>
       <c r="Q59" s="26" t="n"/>
@@ -9896,7 +10853,7 @@
       </c>
       <c r="J66" s="26" t="inlineStr">
         <is>
-          <t>The real Figma photo (Text_Search.png, brightened to view — see QnA-16) shows the Filter sheet DOES have a fixed bottom action bar: a "Reset" (outline) button on the left and an "Apply" (solid red, full width) button on the right. This CONTRADICTS the storyboard PPTX's own note (Open item #3), which says this bar is MISSING. This test case follows the real Figma photo (bar is present); final Pass/Fail is on hold until BA confirms which source is correct. See QnA-18.</t>
+          <t>The real Figma photo (Text Search.png) AND the updated storyboard (v0.1-20260819) now agree: the Filter sheet DOES have a fixed bottom action bar with a "Reset" (outline) button on the left and an "Apply" (solid red, full-width) button on the right, always visible regardless of scroll position (sticky). The source conflict is resolved — this can now be scored Pass/Fail normally. See QnA-18 (now Resolved).</t>
         </is>
       </c>
       <c r="K66" s="26" t="inlineStr">
@@ -9907,7 +10864,7 @@
       <c r="L66" s="28" t="n"/>
       <c r="M66" s="28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N66" s="28" t="n"/>
@@ -9919,7 +10876,7 @@
       </c>
       <c r="Q66" s="26" t="inlineStr">
         <is>
-          <t>Found by comparing the real Figma photo (brightened) against the PPTX storyboard — the two sources disagree on this one UI detail.</t>
+          <t>RESOLVED — QnA-18: xem chi tiết trong file QnA log. Both sources (Figma + the updated storyboard) now agree.</t>
         </is>
       </c>
     </row>
@@ -11674,7 +12631,7 @@
       </c>
       <c r="J91" s="27" t="inlineStr">
         <is>
-          <t>The system rejects it before uploading, shows the correct format-error Toast per FR-IS-04. No crash, no Loading screen shown.</t>
+          <t>The system rejects the file before uploading, showing the exact FR-IS-04 toast text: "Invalid image format or file size exceeds 5MB. Please try again."; no crash, the Loading Screen never opens.</t>
         </is>
       </c>
       <c r="K91" s="27" t="inlineStr">
@@ -12007,9 +12964,10 @@
       </c>
       <c r="H96" s="27" t="inlineStr">
         <is>
-          <t>1. On the image results page, tap the thumbnail in the search box.
-2. Check that the Crop tool opens.
-3. Drag the rectangle to narrow the scan area, confirm.</t>
+          <t>1. On the image results page, tap the photo thumbnail in the Search Bar.
+2. Check the Crop tool opens.
+3. Drag the rectangle to narrow the scan area, confirm.
+4. Check whether the Search Bar thumbnail changes to match the selected crop region afterward, or still shows the original uncropped photo.</t>
         </is>
       </c>
       <c r="I96" s="27" t="inlineStr">
@@ -12019,7 +12977,7 @@
       </c>
       <c r="J96" s="27" t="inlineStr">
         <is>
-          <t>The Crop overlay tool opens correctly, letting the shopper drag a rectangle to limit the AI scan area. After confirming, the system re-runs the search based on the cropped area.</t>
+          <t>The Crop overlay tool opens correctly, allowing the rectangle to be dragged to limit the AI scan area; after confirming, the system re-runs the search based on the cropped region; the Search Bar thumbnail must also update to show the CROPPED portion of the photo (no longer the full original image) — giving the customer visual confirmation the system is now searching the selected region.</t>
         </is>
       </c>
       <c r="K96" s="27" t="inlineStr">
@@ -12355,9 +13313,10 @@
       <c r="H101" s="27" t="inlineStr">
         <is>
           <t>1. Upload a blurry/out-of-focus photo.
-2. Check the results page.
-3. Tap "Try again".
-4. Go through the image flow again, upload a blurry photo again, this time tap "Search by keyword".</t>
+2. Check the results screen.
+3. Tap "Retry".
+4. Return to the image flow, upload the blurry photo again, this time tap "Search by keyword".
+5. Check the state of the Pre-search screen just navigated to: the search box, the Recent Searches/Trending blocks.</t>
         </is>
       </c>
       <c r="I101" s="27" t="inlineStr">
@@ -12367,7 +13326,7 @@
       </c>
       <c r="J101" s="27" t="inlineStr">
         <is>
-          <t>Step 2: shows the correct "Not recognized" error page with specific recovery tips, without any raw technical error code. Step 3: goes back to the Camera screen, keeping the same front/rear camera mode used before. Step 4: correctly goes to the Pre-search screen.</t>
+          <t>Step 2: correctly shows the "Not recognized" failure screen with specific recovery guidance, no technical error codes. Step 3: returns to the Camera Screen, keeping the previously used front/rear camera mode. Step 4: correctly navigates to the Pre-search Screen (SS-SCR-001) — not back to the Camera Screen like the "Retry" CTA. Step 5: the Pre-search Screen is in a clean, normal state — the search box is empty and ready for new input, the Recent Searches/Trending Search blocks display fully as on a normal Pre-search entry, with no trace of the previous failed image search (no leftover error banner).</t>
         </is>
       </c>
       <c r="K101" s="27" t="inlineStr">
@@ -12621,7 +13580,7 @@
       </c>
       <c r="F105" s="26" t="inlineStr">
         <is>
-          <t>Auto-stop timing — conflict between a fixed 6 seconds and a proposed "2s silence / 15s max"</t>
+          <t>Auto-stop threshold fixed at 6 seconds (confirmed, conflict resolved)</t>
         </is>
       </c>
       <c r="G105" s="26" t="inlineStr">
@@ -12642,7 +13601,7 @@
       </c>
       <c r="J105" s="26" t="inlineStr">
         <is>
-          <t>TBD — the storyboard has 2 conflicting descriptions of this same behavior: the screen description says "auto-stop after H seconds" (Loading), while the "Open items" section instead proposes "2 seconds of silence or 15 seconds max". Do not mark a quantitative Pass/Fail until TD/BA confirms one official value. See QnA-05.</t>
+          <t>The updated storyboard (v0.1-20260819) removed the "2 seconds of silence / 15 seconds max" proposal — only one official value remains: recording auto-stops exactly 6 seconds after it begins, regardless of any pause in the middle. Step 2 (speak, then pause 2 seconds) must NOT trigger an early auto-stop — the system keeps recording until the 6-second mark. See QnA-05 (now Resolved).</t>
         </is>
       </c>
       <c r="K105" s="26" t="inlineStr">
@@ -12653,7 +13612,7 @@
       <c r="L105" s="28" t="n"/>
       <c r="M105" s="28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N105" s="28" t="n"/>
@@ -12665,7 +13624,7 @@
       </c>
       <c r="Q105" s="26" t="inlineStr">
         <is>
-          <t>OPEN — TD needs to confirm the official auto-stop threshold.</t>
+          <t>RESOLVED — QnA-05: xem chi tiết trong file QnA log.</t>
         </is>
       </c>
     </row>
@@ -12950,58 +13909,58 @@
       <c r="Q109" s="27" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="27" t="inlineStr">
+      <c r="A110" s="35" t="inlineStr">
         <is>
           <t>SS-SCR-018-SC1-TC3</t>
         </is>
       </c>
-      <c r="B110" s="27" t="inlineStr">
+      <c r="B110" s="35" t="inlineStr">
         <is>
           <t>SS-SCR-018-SC1</t>
         </is>
       </c>
-      <c r="C110" s="27" t="inlineStr">
+      <c r="C110" s="35" t="inlineStr">
         <is>
           <t>SS-SCR-018</t>
         </is>
       </c>
-      <c r="D110" s="27" t="inlineStr">
+      <c r="D110" s="35" t="inlineStr">
         <is>
           <t>FR-VS-04, FR-VS-05</t>
         </is>
       </c>
-      <c r="E110" s="27" t="inlineStr">
+      <c r="E110" s="35" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="F110" s="27" t="inlineStr">
-        <is>
-          <t>Medium-low confidence shows a suggestion banner, same as the Text flow</t>
-        </is>
-      </c>
-      <c r="G110" s="27" t="inlineStr">
+      <c r="F110" s="35" t="inlineStr">
+        <is>
+          <t>Medium-low confidence shows a suggestion banner — TBD whether this feature is in v1 scope</t>
+        </is>
+      </c>
+      <c r="G110" s="35" t="inlineStr">
         <is>
           <t>Voice-to-text processing is done.</t>
         </is>
       </c>
-      <c r="H110" s="27" t="inlineStr">
+      <c r="H110" s="35" t="inlineStr">
         <is>
           <t>1. Simulate speech that gets a medium-low confidence transcript (close but not certain).
 2. Check the results-page UI.</t>
         </is>
       </c>
-      <c r="I110" s="27" t="inlineStr">
+      <c r="I110" s="35" t="inlineStr">
         <is>
           <t>Unclear speech / medium confidence</t>
         </is>
       </c>
-      <c r="J110" s="27" t="inlineStr">
-        <is>
-          <t>Shows a "Did you mean ...?" banner, similar to the Text flow's auto-correct mechanism (SS-SCR-003), instead of directly returning results that might be wrong.</t>
-        </is>
-      </c>
-      <c r="K110" s="27" t="inlineStr">
+      <c r="J110" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the BRD (FR-VS-04/FR-VS-05) does not mention this banner mechanism at all; it only appears in the storyboard's own note. If the feature is confirmed to be in scope: shows a "Did you mean ...?" banner, similar to the Text flow's auto-correct mechanism (SS-SCR-003), instead of directly returning results that might be wrong. Cannot be scored Pass/Fail until BA/TD confirms this feature genuinely exists in v1. See QnA-51.</t>
+        </is>
+      </c>
+      <c r="K110" s="35" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -13009,13 +13968,21 @@
       <c r="L110" s="28" t="n"/>
       <c r="M110" s="28" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N110" s="28" t="n"/>
       <c r="O110" s="28" t="n"/>
-      <c r="P110" s="27" t="n"/>
-      <c r="Q110" s="27" t="n"/>
+      <c r="P110" s="35" t="inlineStr">
+        <is>
+          <t>QnA-51</t>
+        </is>
+      </c>
+      <c r="Q110" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-51: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="27" t="inlineStr">
@@ -13194,7 +14161,8 @@
       <c r="H113" s="27" t="inlineStr">
         <is>
           <t>1. On the voice flow's "Not recognized" screen.
-2. Tap the secondary "Search by keyword" CTA.</t>
+2. Tap the secondary "Search by keyword" CTA.
+3. Check the state of the Pre-search screen just navigated to: the search box, the Recent Searches/Trending blocks.</t>
         </is>
       </c>
       <c r="I113" s="27" t="inlineStr">
@@ -13204,7 +14172,7 @@
       </c>
       <c r="J113" s="27" t="inlineStr">
         <is>
-          <t>Correctly goes to the Pre-search screen (SS-SCR-001). The shopper is never stuck on the error screen with no way to switch to another search method.</t>
+          <t>Correctly goes to the Pre-search Screen (SS-SCR-001) — not back to the recording layer like the "Retry" CTA; the shopper is never stuck on the error screen with no way to switch to another search method. The Pre-search Screen is in a clean, normal state — the search box is empty and ready for new input, the Recent Searches/Trending Search blocks display fully as on a normal Pre-search entry, with no trace of the previous failed voice search (no leftover error banner).</t>
         </is>
       </c>
       <c r="K113" s="27" t="inlineStr">
@@ -13290,6 +14258,4584 @@
       <c r="O114" s="28" t="n"/>
       <c r="P114" s="27" t="n"/>
       <c r="Q114" s="27" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC1</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-003</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>FR-AC-01, FR-AC-03</t>
+        </is>
+      </c>
+      <c r="E115" s="27" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F115" s="27" t="inlineStr">
+        <is>
+          <t>Dismiss the banner via "X" then keep typing appended characters — banner must not reappear (respect the user's dismissal)</t>
+        </is>
+      </c>
+      <c r="G115" s="27" t="inlineStr">
+        <is>
+          <t>The correction banner is currently shown for "sua toui" (suggesting "sữa tươi").</t>
+        </is>
+      </c>
+      <c r="H115" s="27" t="inlineStr">
+        <is>
+          <t>1. Type "sua toui", wait for the banner to appear.
+2. Tap the "X" to dismiss the banner.
+3. Keep typing characters appended to the saved phrase, e.g. into "sua toui tuoi" (nothing deleted, only appended).
+4. Check whether the banner reappears.
+5. Backspace a few characters until the original saved phrase is broken (e.g. back down to "sua to").
+6. Check the banner state after step 5.</t>
+        </is>
+      </c>
+      <c r="I115" s="27" t="inlineStr">
+        <is>
+          <t>"sua toui" -&gt; X -&gt; "sua toui tuoi" -&gt; backspace down to "sua to"</t>
+        </is>
+      </c>
+      <c r="J115" s="27" t="inlineStr">
+        <is>
+          <t>Step 4: the banner does NOT reappear even though the string still fully contains the previously-dismissed "sua toui" — the system respects the customer's dismissal as long as they are only appending. Step 6: once backspacing breaks the saved phrase, the "dismissed" state resets — if the remaining string still fuzzy-matches, the banner is free to reappear normally.</t>
+        </is>
+      </c>
+      <c r="K115" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L115" s="28" t="n"/>
+      <c r="M115" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N115" s="28" t="n"/>
+      <c r="O115" s="28" t="n"/>
+      <c r="P115" s="27" t="n"/>
+      <c r="Q115" s="27" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B116" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC1</t>
+        </is>
+      </c>
+      <c r="C116" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-003</t>
+        </is>
+      </c>
+      <c r="D116" s="27" t="inlineStr">
+        <is>
+          <t>FR-AC-01, FR-AC-03</t>
+        </is>
+      </c>
+      <c r="E116" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F116" s="27" t="inlineStr">
+        <is>
+          <t>The banner's suggested keyword is guaranteed to return &gt;=1 Active SKU</t>
+        </is>
+      </c>
+      <c r="G116" s="27" t="inlineStr">
+        <is>
+          <t>The fuzzy matcher is active; the catalogue has an active SKU matching the corrected keyword.</t>
+        </is>
+      </c>
+      <c r="H116" s="27" t="inlineStr">
+        <is>
+          <t>1. Type "sua toui", wait for the banner suggesting "sữa tươi".
+2. Tap the corrected-keyword link on the banner.
+3. Check the results page returned.
+4. Check the count of Active-status products in the results.</t>
+        </is>
+      </c>
+      <c r="I116" s="27" t="inlineStr">
+        <is>
+          <t>"sua toui" -&gt; tap "sữa tươi"</t>
+        </is>
+      </c>
+      <c r="J116" s="27" t="inlineStr">
+        <is>
+          <t>The results page returns &gt;=1 product in Active status (still on sale) for the corrected keyword; the system must never suggest a "more accurate" term that leads to a Zero Result or an all-Inactive SKU set — the banner may only suggest phrases already validated to have &gt;=1 Active SKU in the catalogue.</t>
+        </is>
+      </c>
+      <c r="K116" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L116" s="28" t="n"/>
+      <c r="M116" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N116" s="28" t="n"/>
+      <c r="O116" s="28" t="n"/>
+      <c r="P116" s="27" t="n"/>
+      <c r="Q116" s="27" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B117" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4</t>
+        </is>
+      </c>
+      <c r="C117" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-003</t>
+        </is>
+      </c>
+      <c r="D117" s="35" t="inlineStr">
+        <is>
+          <t>FR-AC-01, FR-AC-03</t>
+        </is>
+      </c>
+      <c r="E117" s="35" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F117" s="35" t="inlineStr">
+        <is>
+          <t>Bilingual suggestion when typing English/Russian while UI=VI — behavior TBD</t>
+        </is>
+      </c>
+      <c r="G117" s="35" t="inlineStr">
+        <is>
+          <t>UI language = VI; "moloko" (Russian for "milk") or "milk" (English) is typed into the search box.</t>
+        </is>
+      </c>
+      <c r="H117" s="35" t="inlineStr">
+        <is>
+          <t>1. Set UI language = VI.
+2. Type "milk" (English, correctly spelled).
+3. Check the banner/suggestion content.
+4. Repeat with the Russian word "moloko".</t>
+        </is>
+      </c>
+      <c r="I117" s="35" t="inlineStr">
+        <is>
+          <t>"milk" / "moloko" (UI=VI)</t>
+        </is>
+      </c>
+      <c r="J117" s="35" t="inlineStr">
+        <is>
+          <t>TBD — not yet confirmed: does the banner show both a suggestion in the language being typed (English/Russian, shown first) AND an equivalent Vietnamese suggestion ("sữa") at the same time? Minimum requirement: no crash, and the system returns results relevant to "sữa" regardless of how the suggestion is displayed. See QnA-36.</t>
+        </is>
+      </c>
+      <c r="K117" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L117" s="28" t="n"/>
+      <c r="M117" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N117" s="28" t="n"/>
+      <c r="O117" s="28" t="n"/>
+      <c r="P117" s="35" t="inlineStr">
+        <is>
+          <t>QnA-36</t>
+        </is>
+      </c>
+      <c r="Q117" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-36: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="B118" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4</t>
+        </is>
+      </c>
+      <c r="C118" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-003</t>
+        </is>
+      </c>
+      <c r="D118" s="35" t="inlineStr">
+        <is>
+          <t>FR-AC-01, FR-AC-03</t>
+        </is>
+      </c>
+      <c r="E118" s="35" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F118" s="35" t="inlineStr">
+        <is>
+          <t>Misspelled diacritic-free Vietnamese — suggestion paired with a synonym/related-term equivalent</t>
+        </is>
+      </c>
+      <c r="G118" s="35" t="inlineStr">
+        <is>
+          <t>UI language = VI; "sua tuoiii" is a typo (extra character) of "sua tuoi" (diacritic-free form of "sữa tươi").</t>
+        </is>
+      </c>
+      <c r="H118" s="35" t="inlineStr">
+        <is>
+          <t>1. Set UI language = VI.
+2. Type "sua tuoiii" (diacritic-free, misspelled).
+3. Check the banner suggestion.
+4. Check whether the banner also suggests a synonym/related term with the same meaning (e.g. "fresh milk", "sữa nước") in addition to the direct spelling correction.</t>
+        </is>
+      </c>
+      <c r="I118" s="35" t="inlineStr">
+        <is>
+          <t>"sua tuoiii"</t>
+        </is>
+      </c>
+      <c r="J118" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the banner must correctly suggest "sữa tươi" (spelling correction + diacritic normalization, per FR-SM-06). Whether the banner itself should also surface a synonym/related-term suggestion (as opposed to the system silently expanding synonyms when computing results per FR-SM-04) is not clearly defined for this specific UI element. See QnA-36.</t>
+        </is>
+      </c>
+      <c r="K118" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L118" s="28" t="n"/>
+      <c r="M118" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N118" s="28" t="n"/>
+      <c r="O118" s="28" t="n"/>
+      <c r="P118" s="35" t="inlineStr">
+        <is>
+          <t>QnA-36</t>
+        </is>
+      </c>
+      <c r="Q118" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-36: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B119" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1</t>
+        </is>
+      </c>
+      <c r="C119" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D119" s="35" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-02, FR-PR-05, FR-PR-07, FR-SF-01</t>
+        </is>
+      </c>
+      <c r="E119" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F119" s="35" t="inlineStr">
+        <is>
+          <t>View mode (Grid/List) when a Member logs in for the first time on a different device — sync behavior TBD</t>
+        </is>
+      </c>
+      <c r="G119" s="35" t="inlineStr">
+        <is>
+          <t>The Member has previously selected List view on Device A (saved in Device A's Local Storage).</t>
+        </is>
+      </c>
+      <c r="H119" s="35" t="inlineStr">
+        <is>
+          <t>1. On Device A, log in as the Member, switch view mode to List.
+2. Log in with the same Member account on Device B (never opened the app/searched on B before).
+3. Go to the results page for the first time on Device B.
+4. Check the default view mode on Device B.</t>
+        </is>
+      </c>
+      <c r="I119" s="35" t="inlineStr">
+        <is>
+          <t>Same account, List on A, first visit on B</t>
+        </is>
+      </c>
+      <c r="J119" s="35" t="inlineStr">
+        <is>
+          <t>TBD — not yet confirmed whether Device B shows the mode saved on Device A (account-level server-side sync) or defaults to Grid (per its own device-local state), since FR-PR-07 only says the mode is saved to the device's Local Storage and does not mention cross-device sync. Cannot be scored Pass/Fail until confirmed. See QnA-34.</t>
+        </is>
+      </c>
+      <c r="K119" s="35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L119" s="28" t="n"/>
+      <c r="M119" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N119" s="28" t="n"/>
+      <c r="O119" s="28" t="n"/>
+      <c r="P119" s="35" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="Q119" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-34: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B120" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1</t>
+        </is>
+      </c>
+      <c r="C120" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D120" s="35" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-02, FR-PR-05, FR-PR-07, FR-SF-01</t>
+        </is>
+      </c>
+      <c r="E120" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F120" s="35" t="inlineStr">
+        <is>
+          <t>View mode when two different accounts log in one after another on the same device — inheritance TBD</t>
+        </is>
+      </c>
+      <c r="G120" s="35" t="inlineStr">
+        <is>
+          <t>A shared device; Account 1 has previously selected List on this device.</t>
+        </is>
+      </c>
+      <c r="H120" s="35" t="inlineStr">
+        <is>
+          <t>1. Account 1 logs in on the device, switches view mode to List, then logs out.
+2. Account 2 logs in on the same device (Account 2 has never changed view mode before).
+3. Go to the results page.
+4. Check the default view mode for Account 2.</t>
+        </is>
+      </c>
+      <c r="I120" s="35" t="inlineStr">
+        <is>
+          <t>Account 1 (List) logs out -&gt; Account 2 logs in, same device</t>
+        </is>
+      </c>
+      <c r="J120" s="35" t="inlineStr">
+        <is>
+          <t>TBD — not yet confirmed whether Account 2 inherits List (since it is stored per-device, not per-account) or has its own state (defaulting to Grid). Cannot be scored Pass/Fail until confirmed. See QnA-34.</t>
+        </is>
+      </c>
+      <c r="K120" s="35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L120" s="28" t="n"/>
+      <c r="M120" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N120" s="28" t="n"/>
+      <c r="O120" s="28" t="n"/>
+      <c r="P120" s="35" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="Q120" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-34: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3-TC3</t>
+        </is>
+      </c>
+      <c r="B121" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3</t>
+        </is>
+      </c>
+      <c r="C121" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D121" s="35" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-02, FR-PR-05, FR-PR-07, FR-SF-01</t>
+        </is>
+      </c>
+      <c r="E121" s="35" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F121" s="35" t="inlineStr">
+        <is>
+          <t>State of the results page behind the Autocomplete layer after clearing the keyword via (X) — TBD whether filter/results are kept</t>
+        </is>
+      </c>
+      <c r="G121" s="35" t="inlineStr">
+        <is>
+          <t>The results page has loaded with the "Sugar-free" filter active and "Price low-to-high" sort applied.</t>
+        </is>
+      </c>
+      <c r="H121" s="35" t="inlineStr">
+        <is>
+          <t>1. On the "milk" results page with "Sugar-free" filter + "Price low-to-high" sort applied.
+2. Tap (X) on the Search Bar.
+3. Without typing a new keyword, tap outside or press Back to close the Autocomplete layer.
+4. Check whether the results page reappears, and whether the "Sugar-free" filter chip/sort are still applied.</t>
+        </is>
+      </c>
+      <c r="I121" s="35" t="inlineStr">
+        <is>
+          <t>"milk" + filter/sort active -&gt; tap (X) -&gt; close Autocomplete without a new search</t>
+        </is>
+      </c>
+      <c r="J121" s="35" t="inlineStr">
+        <is>
+          <t>TBD — not yet confirmed whether (a) the results page + filter chip + sort are preserved behind the layer and reappear exactly as before when Autocomplete is closed without a new search, or (b) everything is cleared/reset as soon as (X) is tapped regardless of whether a new search follows. Cannot be scored Pass/Fail until confirmed. See QnA-33.</t>
+        </is>
+      </c>
+      <c r="K121" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L121" s="28" t="n"/>
+      <c r="M121" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N121" s="28" t="n"/>
+      <c r="O121" s="28" t="n"/>
+      <c r="P121" s="35" t="inlineStr">
+        <is>
+          <t>QnA-33</t>
+        </is>
+      </c>
+      <c r="Q121" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-33: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3-TC4</t>
+        </is>
+      </c>
+      <c r="B122" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3</t>
+        </is>
+      </c>
+      <c r="C122" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D122" s="27" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-02, FR-PR-05, FR-PR-07, FR-SF-01</t>
+        </is>
+      </c>
+      <c r="E122" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F122" s="27" t="inlineStr">
+        <is>
+          <t>Tapping the (+) button on a Product Card adds to cart right on the results page, without accidentally opening the PDP</t>
+        </is>
+      </c>
+      <c r="G122" s="27" t="inlineStr">
+        <is>
+          <t>The results page has loaded with &gt;=1 in-stock product.</t>
+        </is>
+      </c>
+      <c r="H122" s="27" t="inlineStr">
+        <is>
+          <t>1. On the "milk" results page, tap precisely on the (+) button of a Product Card (not the image/name area).
+2. Check the UI immediately after tapping.
+3. Confirm the current page is still the results page (not navigated to the PDP).</t>
+        </is>
+      </c>
+      <c r="I122" s="27" t="inlineStr">
+        <is>
+          <t>Tap (+) on 1 in-stock card</t>
+        </is>
+      </c>
+      <c r="J122" s="27" t="inlineStr">
+        <is>
+          <t>The cart badge increments immediately (optimistic update), and a confirmation Toast appears (full behavior already covered in detail in SS-SCR-011); does NOT navigate to the PDP; the (+) tap target is fully separate from the PDP tap target already tested in SC3-TC1.</t>
+        </is>
+      </c>
+      <c r="K122" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L122" s="28" t="n"/>
+      <c r="M122" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N122" s="28" t="n"/>
+      <c r="O122" s="28" t="n"/>
+      <c r="P122" s="27" t="n"/>
+      <c r="Q122" s="27" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC7-TC1</t>
+        </is>
+      </c>
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC7</t>
+        </is>
+      </c>
+      <c r="C123" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D123" s="27" t="inlineStr">
+        <is>
+          <t>FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E123" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F123" s="27" t="inlineStr">
+        <is>
+          <t>Default sort = "Most Relevant" on first entry to the results page</t>
+        </is>
+      </c>
+      <c r="G123" s="27" t="inlineStr">
+        <is>
+          <t>The customer has not selected a Sort option in the current session.</t>
+        </is>
+      </c>
+      <c r="H123" s="27" t="inlineStr">
+        <is>
+          <t>1. Search "milk" for the first time in the session (Sort sheet never opened before).
+2. Check the label on the sticky Sort bar.
+3. Open the Sort bottom sheet (SS-SCR-008), check which option is marked as selected.</t>
+        </is>
+      </c>
+      <c r="I123" s="27" t="inlineStr">
+        <is>
+          <t>"milk" (first time in the session)</t>
+        </is>
+      </c>
+      <c r="J123" s="27" t="inlineStr">
+        <is>
+          <t>The sticky label correctly shows "Most Relevant" from the start; when the Sort sheet is opened, "Most Relevant" is already checked/selected without any prior action from the customer.</t>
+        </is>
+      </c>
+      <c r="K123" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L123" s="28" t="n"/>
+      <c r="M123" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N123" s="28" t="n"/>
+      <c r="O123" s="28" t="n"/>
+      <c r="P123" s="27" t="n"/>
+      <c r="Q123" s="27" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC8-TC1</t>
+        </is>
+      </c>
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC8</t>
+        </is>
+      </c>
+      <c r="C124" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D124" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E124" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F124" s="27" t="inlineStr">
+        <is>
+          <t>The "Filter" button is in its default (no badge) state when no condition has been applied</t>
+        </is>
+      </c>
+      <c r="G124" s="27" t="inlineStr">
+        <is>
+          <t>The results page has just loaded; Filter has never been opened/applied.</t>
+        </is>
+      </c>
+      <c r="H124" s="27" t="inlineStr">
+        <is>
+          <t>1. Search "milk", check the "Filter" button on the sticky bar.
+2. Check whether a count badge is shown.
+3. Check that no filter chip is active on the results page.</t>
+        </is>
+      </c>
+      <c r="I124" s="27" t="inlineStr">
+        <is>
+          <t>"milk" (no filter applied)</t>
+        </is>
+      </c>
+      <c r="J124" s="27" t="inlineStr">
+        <is>
+          <t>The "Filter" button shows no badge (or a badge=0 that is fully hidden, matching the end state of SS-SCR-010-SC3); no filter chip is active; the total result count is the full, unfiltered set.</t>
+        </is>
+      </c>
+      <c r="K124" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L124" s="28" t="n"/>
+      <c r="M124" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N124" s="28" t="n"/>
+      <c r="O124" s="28" t="n"/>
+      <c r="P124" s="27" t="n"/>
+      <c r="Q124" s="27" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9-TC1</t>
+        </is>
+      </c>
+      <c r="B125" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9</t>
+        </is>
+      </c>
+      <c r="C125" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D125" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-02, FR-SF-03</t>
+        </is>
+      </c>
+      <c r="E125" s="27" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="F125" s="27" t="inlineStr">
+        <is>
+          <t>Tapping 1 Smart Filter Chip applies the filter immediately, without opening the detailed Filter sheet</t>
+        </is>
+      </c>
+      <c r="G125" s="27" t="inlineStr">
+        <is>
+          <t>The results page has loaded with the Smart Filter Chips row showing &gt;=1 chip.</t>
+        </is>
+      </c>
+      <c r="H125" s="27" t="inlineStr">
+        <is>
+          <t>1. Search "milk", check the horizontal Smart Filter Chips row above the results grid.
+2. Tap any chip (e.g. "Organic").
+3. Check the chip state, the Filter button badge, and the result count.</t>
+        </is>
+      </c>
+      <c r="I125" s="27" t="inlineStr">
+        <is>
+          <t>Tap the "Organic" chip</t>
+        </is>
+      </c>
+      <c r="J125" s="27" t="inlineStr">
+        <is>
+          <t>The chip switches to an active state (background color changes) immediately on tap, with no separate "Apply" button needed; results update in real time to only matching SKUs; the "Filter" button badge increments by 1; the filtered result count is always &gt;=1 product (per FR-SF-01-&gt;03).</t>
+        </is>
+      </c>
+      <c r="K125" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L125" s="28" t="n"/>
+      <c r="M125" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N125" s="28" t="n"/>
+      <c r="O125" s="28" t="n"/>
+      <c r="P125" s="27" t="n"/>
+      <c r="Q125" s="27" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9-TC2</t>
+        </is>
+      </c>
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9</t>
+        </is>
+      </c>
+      <c r="C126" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D126" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-02, FR-SF-03</t>
+        </is>
+      </c>
+      <c r="E126" s="27" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="F126" s="27" t="inlineStr">
+        <is>
+          <t>Tapping a second chip combines filter conditions (AND) on the Smart Filter Chips</t>
+        </is>
+      </c>
+      <c r="G126" s="27" t="inlineStr">
+        <is>
+          <t>The "Organic" chip is already active.</t>
+        </is>
+      </c>
+      <c r="H126" s="27" t="inlineStr">
+        <is>
+          <t>1. From the "Organic"-filtered state, tap the "Sugar-free" chip as well.
+2. Check the results and badge once both chips are active.
+3. Deselect the "Organic" chip, check that results now only reflect "Sugar-free".</t>
+        </is>
+      </c>
+      <c r="I126" s="27" t="inlineStr">
+        <is>
+          <t>"Organic" + "Sugar-free" chips, then deselect "Organic"</t>
+        </is>
+      </c>
+      <c r="J126" s="27" t="inlineStr">
+        <is>
+          <t>Both active chips apply a combined (AND) filter; badge = 2; deselecting one chip keeps the other, results automatically update to reflect only the remaining active condition, and the badge drops to 1 — consistent with the chip-removal behavior already tested in SS-SCR-010-SC2.</t>
+        </is>
+      </c>
+      <c r="K126" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L126" s="28" t="n"/>
+      <c r="M126" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N126" s="28" t="n"/>
+      <c r="O126" s="28" t="n"/>
+      <c r="P126" s="27" t="n"/>
+      <c r="Q126" s="27" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B127" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC1</t>
+        </is>
+      </c>
+      <c r="C127" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D127" s="35" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-07</t>
+        </is>
+      </c>
+      <c r="E127" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F127" s="35" t="inlineStr">
+        <is>
+          <t>List view when a Member logs in for the first time on a different device — sync behavior TBD (parallel to SS-SCR-005-SC1-TC3)</t>
+        </is>
+      </c>
+      <c r="G127" s="35" t="inlineStr">
+        <is>
+          <t>The Member has previously selected List on Device A.</t>
+        </is>
+      </c>
+      <c r="H127" s="35" t="inlineStr">
+        <is>
+          <t>1. On Device A, switch view mode to List.
+2. Log in with the same account on Device B (first time).
+3. Go to the results page on Device B, check the default view mode.</t>
+        </is>
+      </c>
+      <c r="I127" s="35" t="inlineStr">
+        <is>
+          <t>Same mechanism as SS-SCR-005-SC1-TC3, re-verified from the List/new-device angle</t>
+        </is>
+      </c>
+      <c r="J127" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the same open question as SS-SCR-005-SC1-TC3, since both screens share a single persistence mechanism per FR-PR-07. Cannot be scored Pass/Fail until confirmed. See QnA-34.</t>
+        </is>
+      </c>
+      <c r="K127" s="35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L127" s="28" t="n"/>
+      <c r="M127" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N127" s="28" t="n"/>
+      <c r="O127" s="28" t="n"/>
+      <c r="P127" s="35" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="Q127" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-34: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B128" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC1</t>
+        </is>
+      </c>
+      <c r="C128" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D128" s="35" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-07</t>
+        </is>
+      </c>
+      <c r="E128" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F128" s="35" t="inlineStr">
+        <is>
+          <t>List view when two accounts log in one after another on the same device — inheritance TBD (parallel to SS-SCR-005-SC1-TC4)</t>
+        </is>
+      </c>
+      <c r="G128" s="35" t="inlineStr">
+        <is>
+          <t>Account 1 has selected List on the shared device.</t>
+        </is>
+      </c>
+      <c r="H128" s="35" t="inlineStr">
+        <is>
+          <t>1. Account 1 selects List, logs out.
+2. Account 2 logs in on the same device, goes to the results page.
+3. Check the default view mode for Account 2.</t>
+        </is>
+      </c>
+      <c r="I128" s="35" t="inlineStr">
+        <is>
+          <t>Same mechanism as SS-SCR-005-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="J128" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the same open question as SS-SCR-005-SC1-TC4. Cannot be scored Pass/Fail until confirmed. See QnA-34.</t>
+        </is>
+      </c>
+      <c r="K128" s="35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L128" s="28" t="n"/>
+      <c r="M128" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N128" s="28" t="n"/>
+      <c r="O128" s="28" t="n"/>
+      <c r="P128" s="35" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="Q128" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-34: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B129" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC4</t>
+        </is>
+      </c>
+      <c r="C129" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D129" s="27" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-07</t>
+        </is>
+      </c>
+      <c r="E129" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F129" s="27" t="inlineStr">
+        <is>
+          <t>Tap a Product Card (outside the + button) in List view opens the correct PDP</t>
+        </is>
+      </c>
+      <c r="G129" s="27" t="inlineStr">
+        <is>
+          <t>View mode = List, results page has loaded.</t>
+        </is>
+      </c>
+      <c r="H129" s="27" t="inlineStr">
+        <is>
+          <t>1. On the "milk" results page, List view, tap the image/name area of a product row (not the + button).
+2. Check the page that opens.</t>
+        </is>
+      </c>
+      <c r="I129" s="27" t="inlineStr">
+        <is>
+          <t>Any 1 product row (List)</t>
+        </is>
+      </c>
+      <c r="J129" s="27" t="inlineStr">
+        <is>
+          <t>Opens the correct PDP for the tapped product, consistent with SS-SCR-005-SC3-TC1 (Grid); does not accidentally trigger add-to-cart.</t>
+        </is>
+      </c>
+      <c r="K129" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L129" s="28" t="n"/>
+      <c r="M129" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N129" s="28" t="n"/>
+      <c r="O129" s="28" t="n"/>
+      <c r="P129" s="27" t="n"/>
+      <c r="Q129" s="27" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC5-TC1</t>
+        </is>
+      </c>
+      <c r="B130" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC5</t>
+        </is>
+      </c>
+      <c r="C130" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D130" s="35" t="inlineStr">
+        <is>
+          <t>No clear FR ID in the BRD — see QnA-10</t>
+        </is>
+      </c>
+      <c r="E130" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F130" s="35" t="inlineStr">
+        <is>
+          <t>Tap the (+) button to add to cart in List view, without accidentally opening the PDP</t>
+        </is>
+      </c>
+      <c r="G130" s="35" t="inlineStr">
+        <is>
+          <t>View mode = List, &gt;=1 in-stock product.</t>
+        </is>
+      </c>
+      <c r="H130" s="35" t="inlineStr">
+        <is>
+          <t>1. On the "milk" results page, List view, tap precisely on the (+) button of a product row.
+2. Check the cart badge and the confirmation Toast.
+3. Confirm still on the results page (not navigated to the PDP).</t>
+        </is>
+      </c>
+      <c r="I130" s="35" t="inlineStr">
+        <is>
+          <t>Tap (+) on 1 in-stock row (List)</t>
+        </is>
+      </c>
+      <c r="J130" s="35" t="inlineStr">
+        <is>
+          <t>The badge increments immediately, the confirmation Toast appears (full behavior already tested in SS-SCR-011); does not navigate to the PDP; consistent with SS-SCR-005-SC3-TC4 (Grid).</t>
+        </is>
+      </c>
+      <c r="K130" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L130" s="28" t="n"/>
+      <c r="M130" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N130" s="28" t="n"/>
+      <c r="O130" s="28" t="n"/>
+      <c r="P130" s="35" t="inlineStr">
+        <is>
+          <t>QnA-10</t>
+        </is>
+      </c>
+      <c r="Q130" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-10: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B131" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C131" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D131" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E131" s="35" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F131" s="35" t="inlineStr">
+        <is>
+          <t>Verify "Most Relevant" does not silently fall back to another sort order (AI ranking sanity check)</t>
+        </is>
+      </c>
+      <c r="G131" s="35" t="inlineStr">
+        <is>
+          <t>The "milk" results have several products with different prices/ratings/discount levels.</t>
+        </is>
+      </c>
+      <c r="H131" s="35" t="inlineStr">
+        <is>
+          <t>1. Search "milk", keep the default sort "Most Relevant".
+2. Record the order of the Top 10 products.
+3. Compare this order against the order under Price-ascending and under Name A-Z.
+4. Confirm the "Most Relevant" order does not fully match either of those two simple sorts.</t>
+        </is>
+      </c>
+      <c r="I131" s="35" t="inlineStr">
+        <is>
+          <t>"milk" (Top 10)</t>
+        </is>
+      </c>
+      <c r="J131" s="35" t="inlineStr">
+        <is>
+          <t>The Top 10 order under "Most Relevant" differs from the Price-ascending order and from the Name A-Z order (barring rare coincidental matches) — confirming the system is applying AI Scorecard Ranking (Relevance/Purchase Affinity/Margin/Promotion/Trending per the BRD) rather than silently falling back to a simple sort. The exact weighting cannot be independently verified by QC. See QnA-37.</t>
+        </is>
+      </c>
+      <c r="K131" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L131" s="28" t="n"/>
+      <c r="M131" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N131" s="28" t="n"/>
+      <c r="O131" s="28" t="n"/>
+      <c r="P131" s="35" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q131" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B132" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C132" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D132" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E132" s="35" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F132" s="35" t="inlineStr">
+        <is>
+          <t>Verify "Best Selling" sorts by highest purchase count, descending</t>
+        </is>
+      </c>
+      <c r="G132" s="35" t="inlineStr">
+        <is>
+          <t>Purchase/order count data differs across SKUs in the result set.</t>
+        </is>
+      </c>
+      <c r="H132" s="35" t="inlineStr">
+        <is>
+          <t>1. Search "milk", select Sort = "Best Selling".
+2. Record the purchase count (if exposed via API/admin) of the first 5 SKUs.
+3. Confirm descending order.</t>
+        </is>
+      </c>
+      <c r="I132" s="35" t="inlineStr">
+        <is>
+          <t>Sort = "Best Selling"</t>
+        </is>
+      </c>
+      <c r="J132" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the first 5 SKUs must show a continuously descending purchase count (each SKU &lt;= the previous one); not yet confirmed whether "purchase count" is Order Count (as in FR-PS-03) or Item Quantity, and over what time window (all-time or rolling). See QnA-37.</t>
+        </is>
+      </c>
+      <c r="K132" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L132" s="28" t="n"/>
+      <c r="M132" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N132" s="28" t="n"/>
+      <c r="O132" s="28" t="n"/>
+      <c r="P132" s="35" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q132" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B133" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C133" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D133" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E133" s="35" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F133" s="35" t="inlineStr">
+        <is>
+          <t>Verify "Most Viewed" sorts by view/interest count, descending</t>
+        </is>
+      </c>
+      <c r="G133" s="35" t="inlineStr">
+        <is>
+          <t>Product view count (page view/PDP view) data differs across SKUs.</t>
+        </is>
+      </c>
+      <c r="H133" s="35" t="inlineStr">
+        <is>
+          <t>1. Search "milk", select Sort = "Most Viewed".
+2. Record the view count of the first 5 SKUs (if exposed).
+3. Confirm descending order.</t>
+        </is>
+      </c>
+      <c r="I133" s="35" t="inlineStr">
+        <is>
+          <t>Sort = "Most Viewed"</t>
+        </is>
+      </c>
+      <c r="J133" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the first 5 SKUs should descend by view count; not yet clear whether "most viewed" is PDP views, search-result impressions, or both, and over what time window. See QnA-37.</t>
+        </is>
+      </c>
+      <c r="K133" s="35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L133" s="28" t="n"/>
+      <c r="M133" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N133" s="28" t="n"/>
+      <c r="O133" s="28" t="n"/>
+      <c r="P133" s="35" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q133" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC6</t>
+        </is>
+      </c>
+      <c r="B134" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C134" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D134" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E134" s="27" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F134" s="27" t="inlineStr">
+        <is>
+          <t>Verify "Biggest Discount" sorts by discount %, descending</t>
+        </is>
+      </c>
+      <c r="G134" s="27" t="inlineStr">
+        <is>
+          <t>SKUs in the result set have varying discount % (including SKUs at 0% discount).</t>
+        </is>
+      </c>
+      <c r="H134" s="27" t="inlineStr">
+        <is>
+          <t>1. Search "milk", select Sort = "Biggest Discount".
+2. Record the discount % shown on the badge for the first 5-10 SKUs.
+3. Confirm descending %; check that 0%-discount SKUs are pushed to the end.</t>
+        </is>
+      </c>
+      <c r="I134" s="27" t="inlineStr">
+        <is>
+          <t>Sort = "Biggest Discount"</t>
+        </is>
+      </c>
+      <c r="J134" s="27" t="inlineStr">
+        <is>
+          <t>The discount % descends continuously from the first SKU; SKUs with no promotion (0%) sit at the end of the list, not interleaved with discounted SKUs.</t>
+        </is>
+      </c>
+      <c r="K134" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L134" s="28" t="n"/>
+      <c r="M134" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N134" s="28" t="n"/>
+      <c r="O134" s="28" t="n"/>
+      <c r="P134" s="27" t="n"/>
+      <c r="Q134" s="27" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC7</t>
+        </is>
+      </c>
+      <c r="B135" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C135" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D135" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E135" s="35" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F135" s="35" t="inlineStr">
+        <is>
+          <t>Verify "Highest Rated" sorts by average star rating, descending</t>
+        </is>
+      </c>
+      <c r="G135" s="35" t="inlineStr">
+        <is>
+          <t>SKUs have varying average ratings and review counts (including a 5-star/1-review SKU and a 4.8-star/1000-review SKU).</t>
+        </is>
+      </c>
+      <c r="H135" s="35" t="inlineStr">
+        <is>
+          <t>1. Search "milk", select Sort = "Highest Rated".
+2. Record the average rating of the first 5-10 SKUs.
+3. Check whether an SKU with very few reviews (e.g. 1 review, 5 stars) ranks above an SKU with many more reviews but a slightly lower average.</t>
+        </is>
+      </c>
+      <c r="I135" s="35" t="inlineStr">
+        <is>
+          <t>Sort = "Highest Rated"</t>
+        </is>
+      </c>
+      <c r="J135" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the average rating must descend; not yet confirmed whether a review-count-weighted/Bayesian smoothing is applied to prevent a 1-review 5-star SKU from dominating over a higher-review SKU with a slightly lower average, or whether the raw average is used as-is. See QnA-37.</t>
+        </is>
+      </c>
+      <c r="K135" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L135" s="28" t="n"/>
+      <c r="M135" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N135" s="28" t="n"/>
+      <c r="O135" s="28" t="n"/>
+      <c r="P135" s="35" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q135" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC8</t>
+        </is>
+      </c>
+      <c r="B136" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C136" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D136" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E136" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F136" s="35" t="inlineStr">
+        <is>
+          <t>Verify "Price: Low to High" sorts by ascending price, with tie handling</t>
+        </is>
+      </c>
+      <c r="G136" s="35" t="inlineStr">
+        <is>
+          <t>There are &gt;=2 SKUs with the exact same price in the result set.</t>
+        </is>
+      </c>
+      <c r="H136" s="35" t="inlineStr">
+        <is>
+          <t>1. Search "milk", select Sort = "Price: Low to High".
+2. Record the price of the full Top 10.
+3. Confirm the price ascends continuously (each SKU &gt;= the previous one).
+4. For SKUs with identical prices, note the current tie-break order.</t>
+        </is>
+      </c>
+      <c r="I136" s="35" t="inlineStr">
+        <is>
+          <t>Sort = "Price: Low to High"</t>
+        </is>
+      </c>
+      <c r="J136" s="35" t="inlineStr">
+        <is>
+          <t>TBD — price must ascend continuously across the whole list; the tie-break rule for SKUs with the exact same price (by Relevance? by SKU creation date? by Product ID?) is not defined in the BRD. See QnA-37.</t>
+        </is>
+      </c>
+      <c r="K136" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L136" s="28" t="n"/>
+      <c r="M136" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N136" s="28" t="n"/>
+      <c r="O136" s="28" t="n"/>
+      <c r="P136" s="35" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q136" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC9</t>
+        </is>
+      </c>
+      <c r="B137" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C137" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D137" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E137" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F137" s="27" t="inlineStr">
+        <is>
+          <t>Verify "Price: High to Low" sorts by descending price</t>
+        </is>
+      </c>
+      <c r="G137" s="27" t="inlineStr">
+        <is>
+          <t>The result set spans a wide price range.</t>
+        </is>
+      </c>
+      <c r="H137" s="27" t="inlineStr">
+        <is>
+          <t>1. Search "milk", select Sort = "Price: High to Low".
+2. Record the Top 10 prices.
+3. Confirm the price descends continuously, and that the SKU order is exactly the reverse of TC8 ("Price: Low to High") on the same result set.</t>
+        </is>
+      </c>
+      <c r="I137" s="27" t="inlineStr">
+        <is>
+          <t>Sort = "Price: High to Low"</t>
+        </is>
+      </c>
+      <c r="J137" s="27" t="inlineStr">
+        <is>
+          <t>Price descends continuously; the SKU order is exactly the reverse of the "Price: Low to High" sort on the same result set (no SKU out of place).</t>
+        </is>
+      </c>
+      <c r="K137" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L137" s="28" t="n"/>
+      <c r="M137" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N137" s="28" t="n"/>
+      <c r="O137" s="28" t="n"/>
+      <c r="P137" s="27" t="n"/>
+      <c r="Q137" s="27" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC10</t>
+        </is>
+      </c>
+      <c r="B138" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C138" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D138" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E138" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F138" s="27" t="inlineStr">
+        <is>
+          <t>Verify "Product Name (A-Z)" sorts alphabetically, handling Vietnamese diacritics</t>
+        </is>
+      </c>
+      <c r="G138" s="27" t="inlineStr">
+        <is>
+          <t>The result set has SKU names starting with both diacritic and diacritic-free characters, or mixed upper/lower case.</t>
+        </is>
+      </c>
+      <c r="H138" s="27" t="inlineStr">
+        <is>
+          <t>1. Search "milk", select Sort = "Product Name (A-Z)".
+2. Record the names of the top 10-15 SKUs.
+3. Confirm the order follows correct Vietnamese alphabetical collation (diacritics: a, à, á, ả, ã, ạ, ă,... in the correct position per Vietnamese sort order, not raw Unicode code-point order).</t>
+        </is>
+      </c>
+      <c r="I138" s="27" t="inlineStr">
+        <is>
+          <t>Sort = "Product Name (A-Z)"</t>
+        </is>
+      </c>
+      <c r="J138" s="27" t="inlineStr">
+        <is>
+          <t>The order follows correct Vietnamese alphabetical collation, not raw Unicode code-point order (which would incorrectly place diacritic characters after ASCII characters); case does not cause an unreasonable ordering skew.</t>
+        </is>
+      </c>
+      <c r="K138" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L138" s="28" t="n"/>
+      <c r="M138" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N138" s="28" t="n"/>
+      <c r="O138" s="28" t="n"/>
+      <c r="P138" s="27" t="n"/>
+      <c r="Q138" s="27" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="B139" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC2</t>
+        </is>
+      </c>
+      <c r="C139" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D139" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E139" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F139" s="27" t="inlineStr">
+        <is>
+          <t>Tapping the "X" in the Sort sheet header closes it and keeps the previous selection (parallel to the tap-outside behavior in TC1)</t>
+        </is>
+      </c>
+      <c r="G139" s="27" t="inlineStr">
+        <is>
+          <t>The Sort bottom sheet is open, current criterion = "Most Relevant".</t>
+        </is>
+      </c>
+      <c r="H139" s="27" t="inlineStr">
+        <is>
+          <t>1. Open the Sort sheet (currently "Most Relevant" selected).
+2. Tap the "X" in the top-right corner of the sheet header (without selecting a different option, without tapping outside).
+3. Check the label on the sticky bar after the sheet closes.</t>
+        </is>
+      </c>
+      <c r="I139" s="27" t="inlineStr">
+        <is>
+          <t>Tap "X" in the header</t>
+        </is>
+      </c>
+      <c r="J139" s="27" t="inlineStr">
+        <is>
+          <t>The sheet closes; the sticky-bar label is still "Most Relevant"; no new query is triggered — identical to the tap-outside dismissal already tested in SC2-TC1, confirming both dismissal methods (tap outside / X button) are consistent.</t>
+        </is>
+      </c>
+      <c r="K139" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L139" s="28" t="n"/>
+      <c r="M139" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N139" s="28" t="n"/>
+      <c r="O139" s="28" t="n"/>
+      <c r="P139" s="27" t="n"/>
+      <c r="Q139" s="27" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC3-TC2</t>
+        </is>
+      </c>
+      <c r="B140" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC3</t>
+        </is>
+      </c>
+      <c r="C140" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D140" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E140" s="35" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="F140" s="35" t="inlineStr">
+        <is>
+          <t>Verify the Labels chip generation &amp; display-order rule (Information Gain) — TBD</t>
+        </is>
+      </c>
+      <c r="G140" s="35" t="inlineStr">
+        <is>
+          <t>The Labels tab shows a chip list (same data source as the Smart Filter Chips on the results page, per FR-SF-04 "based on the smart filter list").</t>
+        </is>
+      </c>
+      <c r="H140" s="35" t="inlineStr">
+        <is>
+          <t>1. Search "milk", open Filter, switch to the Labels tab.
+2. Record the display order of every chip in the tab.
+3. Compare this order against the Smart Filter Chips row shown directly on the results page (SS-SCR-005-SC9) for the same keyword.
+4. Switch to a different keyword (e.g. "beer"), repeat steps 1-2, and check whether the generated chip set changes to match the new keyword.</t>
+        </is>
+      </c>
+      <c r="I140" s="35" t="inlineStr">
+        <is>
+          <t>"milk" vs "beer"</t>
+        </is>
+      </c>
+      <c r="J140" s="35" t="inlineStr">
+        <is>
+          <t>TBD — FR-SF-03 only states "AI pulls up to 10 smart filter tags with the highest Information Gain... flat structure", with no description of the computation formula, the minimum qualifying threshold, or the display order. Minimum requirement: the chip set must change with the keyword (not static), and the chip order must be consistent between the Labels tab and the Smart Filter Chips row on the results page (same data source). Cannot be scored against a precise Pass/Fail until the formula is confirmed. See QnA-38.</t>
+        </is>
+      </c>
+      <c r="K140" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L140" s="28" t="n"/>
+      <c r="M140" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N140" s="28" t="n"/>
+      <c r="O140" s="28" t="n"/>
+      <c r="P140" s="35" t="inlineStr">
+        <is>
+          <t>QnA-38</t>
+        </is>
+      </c>
+      <c r="Q140" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-38: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6-TC1</t>
+        </is>
+      </c>
+      <c r="B141" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6</t>
+        </is>
+      </c>
+      <c r="C141" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D141" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E141" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F141" s="27" t="inlineStr">
+        <is>
+          <t>The badge on single-select tabs (Category/Delivery/Rating/Price) is always at most 1</t>
+        </is>
+      </c>
+      <c r="G141" s="27" t="inlineStr">
+        <is>
+          <t>No condition selected yet in the 4 single-select tabs (only 1 value per tab).</t>
+        </is>
+      </c>
+      <c r="H141" s="27" t="inlineStr">
+        <is>
+          <t>1. Open Filter.
+2. Select 1 Category branch, check the Category tab badge.
+3. Select 1 Rating level, check the Rating tab badge.
+4. Select 1 Delivery condition and 1 Price range, check both corresponding tab badges.
+5. Select a different Category branch (replacing the first), check whether the Category tab badge increases to 2.</t>
+        </is>
+      </c>
+      <c r="I141" s="27" t="inlineStr">
+        <is>
+          <t>1 selection per tab, then change Category</t>
+        </is>
+      </c>
+      <c r="J141" s="27" t="inlineStr">
+        <is>
+          <t>Each single-select tab correctly shows a badge of "1" with one selection; step 5: switching to a different Category branch does NOT bump the badge to "2" (it stays "1", since it's a replacement, not an addition — consistent with this tab's single-select nature).</t>
+        </is>
+      </c>
+      <c r="K141" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L141" s="28" t="n"/>
+      <c r="M141" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N141" s="28" t="n"/>
+      <c r="O141" s="28" t="n"/>
+      <c r="P141" s="27" t="n"/>
+      <c r="Q141" s="27" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6-TC2</t>
+        </is>
+      </c>
+      <c r="B142" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6</t>
+        </is>
+      </c>
+      <c r="C142" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D142" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E142" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F142" s="27" t="inlineStr">
+        <is>
+          <t>The Labels tab badge (multi-select) correctly counts the number of active chips</t>
+        </is>
+      </c>
+      <c r="G142" s="27" t="inlineStr">
+        <is>
+          <t>No Label chip selected yet.</t>
+        </is>
+      </c>
+      <c r="H142" s="27" t="inlineStr">
+        <is>
+          <t>1. Open Filter, Labels tab.
+2. Select "Sugar-free", "Low-sugar", "Organic" one at a time — check the Labels tab badge after each selection.
+3. Deselect "Low-sugar", check the badge.</t>
+        </is>
+      </c>
+      <c r="I142" s="27" t="inlineStr">
+        <is>
+          <t>Select 3 chips -&gt; deselect 1</t>
+        </is>
+      </c>
+      <c r="J142" s="27" t="inlineStr">
+        <is>
+          <t>The Labels tab badge increases correctly with each chip: 0-&gt;1-&gt;2-&gt;3 after each selection; drops back to 2 after deselecting "Low-sugar" — matching the real Figma reference (3 active chips -&gt; Labels tab badge correctly shows "3").</t>
+        </is>
+      </c>
+      <c r="K142" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L142" s="28" t="n"/>
+      <c r="M142" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N142" s="28" t="n"/>
+      <c r="O142" s="28" t="n"/>
+      <c r="P142" s="27" t="n"/>
+      <c r="Q142" s="27" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6-TC3</t>
+        </is>
+      </c>
+      <c r="B143" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6</t>
+        </is>
+      </c>
+      <c r="C143" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D143" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E143" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F143" s="35" t="inlineStr">
+        <is>
+          <t>Total badge on the "Filter" button on the results page — TBD whether it exists</t>
+        </is>
+      </c>
+      <c r="G143" s="35" t="inlineStr">
+        <is>
+          <t>3 conditions applied (Labels: Sugar-free + Low-sugar + Organic) and "Apply" tapped.</t>
+        </is>
+      </c>
+      <c r="H143" s="35" t="inlineStr">
+        <is>
+          <t>1. Apply the 3 Label chips above, tap "Apply".
+2. Check the "Filter" button on the results page's sticky bar (outside the sheet).
+3. Check whether any count badge is shown next to the "Filter" button.</t>
+        </is>
+      </c>
+      <c r="I143" s="35" t="inlineStr">
+        <is>
+          <t>3 conditions applied</t>
+        </is>
+      </c>
+      <c r="J143" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the real Figma reference (Text Search.png) shows the "Filter" button on the results page WITHOUT any count badge even with 3 conditions applied, contradicting the "Filter button badge = total applied conditions" assumption used in SS-SCR-009-SC1-TC1 and throughout SS-SCR-010. Cannot be scored Pass/Fail until BA/UX confirms which Figma version is authoritative. See QnA-39.</t>
+        </is>
+      </c>
+      <c r="K143" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L143" s="28" t="n"/>
+      <c r="M143" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N143" s="28" t="n"/>
+      <c r="O143" s="28" t="n"/>
+      <c r="P143" s="35" t="inlineStr">
+        <is>
+          <t>QnA-39</t>
+        </is>
+      </c>
+      <c r="Q143" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-39: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7-TC1</t>
+        </is>
+      </c>
+      <c r="B144" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7</t>
+        </is>
+      </c>
+      <c r="C144" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D144" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E144" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F144" s="27" t="inlineStr">
+        <is>
+          <t>"Reset" clears every selection in the sheet; the sheet stays open</t>
+        </is>
+      </c>
+      <c r="G144" s="27" t="inlineStr">
+        <is>
+          <t>Several conditions have been selected across multiple tabs (Category, 3 Labels, Rating) but "Apply" has NOT been tapped yet.</t>
+        </is>
+      </c>
+      <c r="H144" s="27" t="inlineStr">
+        <is>
+          <t>1. Select 1 Category + 3 Label chips + 1 Rating level in Filter (without tapping Apply).
+2. Tap the "Reset" button.
+3. Check the state of every tab (badge, chips, radio buttons) and the sheet state (closed or still open) immediately after the tap.</t>
+        </is>
+      </c>
+      <c r="I144" s="27" t="inlineStr">
+        <is>
+          <t>5 conditions selected -&gt; tap Reset</t>
+        </is>
+      </c>
+      <c r="J144" s="27" t="inlineStr">
+        <is>
+          <t>Every per-tab badge returns to 0/hidden; every selected chip/radio returns to an unselected state; the sheet does NOT auto-close — the customer stays on the Filter sheet with a blank slate to reselect if desired.</t>
+        </is>
+      </c>
+      <c r="K144" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L144" s="28" t="n"/>
+      <c r="M144" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N144" s="28" t="n"/>
+      <c r="O144" s="28" t="n"/>
+      <c r="P144" s="27" t="n"/>
+      <c r="Q144" s="27" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7-TC2</t>
+        </is>
+      </c>
+      <c r="B145" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7</t>
+        </is>
+      </c>
+      <c r="C145" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D145" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E145" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F145" s="27" t="inlineStr">
+        <is>
+          <t>Tapping "Apply" right after "Reset" (0 conditions) returns the full result set</t>
+        </is>
+      </c>
+      <c r="G145" s="27" t="inlineStr">
+        <is>
+          <t>A filter ("Sugar-free") is already active on the results page before reopening Filter.</t>
+        </is>
+      </c>
+      <c r="H145" s="27" t="inlineStr">
+        <is>
+          <t>1. On the results page filtered by "Sugar-free", reopen Filter.
+2. Tap "Reset" (clears "Sugar-free" from the sheet).
+3. Tap "Apply".
+4. Check the results page and the Filter button/tab badges.</t>
+        </is>
+      </c>
+      <c r="I145" s="27" t="inlineStr">
+        <is>
+          <t>Old filter="Sugar-free" -&gt; Reset -&gt; Apply</t>
+        </is>
+      </c>
+      <c r="J145" s="27" t="inlineStr">
+        <is>
+          <t>The sheet closes; the results page returns to the full, unfiltered set (equivalent to the "Clear filters" state in SS-SCR-010-SC3); no "Sugar-free" chip remains active on the results page.</t>
+        </is>
+      </c>
+      <c r="K145" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L145" s="28" t="n"/>
+      <c r="M145" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N145" s="28" t="n"/>
+      <c r="O145" s="28" t="n"/>
+      <c r="P145" s="27" t="n"/>
+      <c r="Q145" s="27" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7-TC3</t>
+        </is>
+      </c>
+      <c r="B146" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7</t>
+        </is>
+      </c>
+      <c r="C146" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D146" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E146" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F146" s="27" t="inlineStr">
+        <is>
+          <t>Tapping "Apply" with no change from the currently-applied state (no-op)</t>
+        </is>
+      </c>
+      <c r="G146" s="27" t="inlineStr">
+        <is>
+          <t>The "Organic" filter is currently applied on the results page.</t>
+        </is>
+      </c>
+      <c r="H146" s="27" t="inlineStr">
+        <is>
+          <t>1. Reopen Filter while "Organic" is active.
+2. Without changing anything, tap "Apply" directly.
+3. Check the UI (any flicker/jank) and the results.</t>
+        </is>
+      </c>
+      <c r="I146" s="27" t="inlineStr">
+        <is>
+          <t>Filter="Organic" unchanged -&gt; tap Apply</t>
+        </is>
+      </c>
+      <c r="J146" s="27" t="inlineStr">
+        <is>
+          <t>The sheet closes normally with no error/UI jank; the results and badges remain unchanged from before the sheet was opened — a no-op behavior consistent with the one already tested in SS-SCR-008-SC3 (reselecting the currently active Sort criterion).</t>
+        </is>
+      </c>
+      <c r="K146" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L146" s="28" t="n"/>
+      <c r="M146" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N146" s="28" t="n"/>
+      <c r="O146" s="28" t="n"/>
+      <c r="P146" s="27" t="n"/>
+      <c r="Q146" s="27" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8-TC1</t>
+        </is>
+      </c>
+      <c r="B147" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8</t>
+        </is>
+      </c>
+      <c r="C147" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D147" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E147" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F147" s="27" t="inlineStr">
+        <is>
+          <t>Tapping a tab correctly swaps the panel content and updates the active state</t>
+        </is>
+      </c>
+      <c r="G147" s="27" t="inlineStr">
+        <is>
+          <t>The Filter sheet has just opened, the "Category" tab is active by default.</t>
+        </is>
+      </c>
+      <c r="H147" s="27" t="inlineStr">
+        <is>
+          <t>1. Open Filter, check that the "Category" tab is active (red left border, bold red text) and the right panel shows Category content.
+2. Tap the "Labels" tab.
+3. Check whether "Labels" becomes active, whether "Category" returns to an inactive state, and whether the right panel switches to Labels content.
+4. Repeat with the "Delivery", "Rating", and "Price" tabs.</t>
+        </is>
+      </c>
+      <c r="I147" s="27" t="inlineStr">
+        <is>
+          <t>Tap each of the 5 tabs in turn</t>
+        </is>
+      </c>
+      <c r="J147" s="27" t="inlineStr">
+        <is>
+          <t>On each tap, exactly 1 tab is marked active (red left border + bold red text), the rest return to their default state; the right panel always shows the content matching the currently active tab, with no lag or leftover content from the previous tab.</t>
+        </is>
+      </c>
+      <c r="K147" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L147" s="28" t="n"/>
+      <c r="M147" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N147" s="28" t="n"/>
+      <c r="O147" s="28" t="n"/>
+      <c r="P147" s="27" t="n"/>
+      <c r="Q147" s="27" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8-TC2</t>
+        </is>
+      </c>
+      <c r="B148" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8</t>
+        </is>
+      </c>
+      <c r="C148" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D148" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E148" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F148" s="27" t="inlineStr">
+        <is>
+          <t>Switching tabs back and forth does not lose the selections/badge of a previously-selected tab</t>
+        </is>
+      </c>
+      <c r="G148" s="27" t="inlineStr">
+        <is>
+          <t>The Filter sheet is open.</t>
+        </is>
+      </c>
+      <c r="H148" s="27" t="inlineStr">
+        <is>
+          <t>1. On the "Labels" tab, select the 2 chips "Sugar-free" and "Organic" (Labels tab badge = 2).
+2. Switch to the "Rating" tab, select "4 stars &amp; up" (Rating tab badge = 1).
+3. Switch to the "Price" tab without selecting anything.
+4. Switch back to the "Labels" tab, check the 2 previously selected chips and the badge.
+5. Switch back to the "Rating" tab, check the selection and the badge.</t>
+        </is>
+      </c>
+      <c r="I148" s="27" t="inlineStr">
+        <is>
+          <t>Labels=2 chips, Rating=1 level, switch through Price and back</t>
+        </is>
+      </c>
+      <c r="J148" s="27" t="inlineStr">
+        <is>
+          <t>After switching through several tabs and back, the "Labels" tab still shows the 2 previously selected chips as active and the badge is still 2; the "Rating" tab still holds the "4 stars &amp; up" selection with badge = 1 — no selection is lost or reset by switching tabs back and forth (it is only cleared by tapping "Reset" or closing via (X), already tested separately in SC7/SC5).</t>
+        </is>
+      </c>
+      <c r="K148" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L148" s="28" t="n"/>
+      <c r="M148" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N148" s="28" t="n"/>
+      <c r="O148" s="28" t="n"/>
+      <c r="P148" s="27" t="n"/>
+      <c r="Q148" s="27" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B149" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4</t>
+        </is>
+      </c>
+      <c r="C149" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D149" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E149" s="27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F149" s="27" t="inlineStr">
+        <is>
+          <t>Selecting a parent category correctly shows "All in [Category name]", applying to the whole subtree</t>
+        </is>
+      </c>
+      <c r="G149" s="27" t="inlineStr">
+        <is>
+          <t>The category tree has &gt;=1 parent branch with several child categories.</t>
+        </is>
+      </c>
+      <c r="H149" s="27" t="inlineStr">
+        <is>
+          <t>1. On the Category tab, drill into "Food &amp; Beverage" &gt; "Milk &amp; Eggs".
+2. Check the first option in the child-category list.
+3. Select it, tap Apply.
+4. Check the scope of the returned results (does it include Fresh Milk, Plant Milk, Soy Milk, Yogurt, and Eggs, or only one specific child category).</t>
+        </is>
+      </c>
+      <c r="I149" s="27" t="inlineStr">
+        <is>
+          <t>Drill into "Milk &amp; Eggs" -&gt; select "All in 'Milk &amp; Eggs'"</t>
+        </is>
+      </c>
+      <c r="J149" s="27" t="inlineStr">
+        <is>
+          <t>The child-category list correctly shows a radio option "All in 'Milk &amp; Eggs'" at the top (pre-selected by default), above the specific child categories (Fresh Milk, Plant Milk, Soy Milk, Yogurt, Eggs) — matching the real Figma reference; selecting this option returns results across the ENTIRE "Milk &amp; Eggs" subtree (all child categories), not narrowed to any single child category.</t>
+        </is>
+      </c>
+      <c r="K149" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L149" s="28" t="n"/>
+      <c r="M149" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N149" s="28" t="n"/>
+      <c r="O149" s="28" t="n"/>
+      <c r="P149" s="27" t="n"/>
+      <c r="Q149" s="27" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="B150" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4</t>
+        </is>
+      </c>
+      <c r="C150" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D150" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E150" s="35" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F150" s="35" t="inlineStr">
+        <is>
+          <t>Tapping the "‹ All categories" breadcrumb — TBD whether it returns to root and clears the Category selection</t>
+        </is>
+      </c>
+      <c r="G150" s="35" t="inlineStr">
+        <is>
+          <t>Currently at a deep child level (e.g. "Food &amp; Beverage &gt; Milk &amp; Eggs") with "All in 'Milk &amp; Eggs'" selected.</t>
+        </is>
+      </c>
+      <c r="H150" s="35" t="inlineStr">
+        <is>
+          <t>1. Drill into "Food &amp; Beverage &gt; Milk &amp; Eggs", select "All in 'Milk &amp; Eggs'" (without tapping Apply yet).
+2. Tap the "‹ All categories" breadcrumb at the top.
+3. Check the list shown afterward (does it return to the correct top level: Food &amp; Beverage, Mom &amp; Baby, Fresh...).
+4. Check the Category tab badge and whether "All in 'Milk &amp; Eggs'" is still marked as selected.</t>
+        </is>
+      </c>
+      <c r="I150" s="35" t="inlineStr">
+        <is>
+          <t>Tap "‹ All categories" after selecting "All in 'Milk &amp; Eggs'"</t>
+        </is>
+      </c>
+      <c r="J150" s="35" t="inlineStr">
+        <is>
+          <t>TBD — not yet confirmed whether tapping "‹ All categories" (a) returns to the top-level category list AND simultaneously clears the current Category selection entirely (badge back to 0), or (b) merely navigates the UI back to root WITHOUT clearing the previously confirmed selection (badge unchanged). Cannot be scored Pass/Fail until confirmed. See QnA-40.</t>
+        </is>
+      </c>
+      <c r="K150" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L150" s="28" t="n"/>
+      <c r="M150" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N150" s="28" t="n"/>
+      <c r="O150" s="28" t="n"/>
+      <c r="P150" s="35" t="inlineStr">
+        <is>
+          <t>QnA-40</t>
+        </is>
+      </c>
+      <c r="Q150" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-40: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="B151" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC2</t>
+        </is>
+      </c>
+      <c r="C151" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D151" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E151" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F151" s="35" t="inlineStr">
+        <is>
+          <t>Verify the 3 percentile price presets (&lt;30% low / 30-70% mid / &gt;70% high) are computed correctly against the current result set</t>
+        </is>
+      </c>
+      <c r="G151" s="35" t="inlineStr">
+        <is>
+          <t>The "milk" result set spans a range of prices, with some SKUs currently on a discount promotion.</t>
+        </is>
+      </c>
+      <c r="H151" s="35" t="inlineStr">
+        <is>
+          <t>1. Search "milk" (128 products), open Filter, Price tab.
+2. Record the specific price range (e.g. "20,000d - 35,000d") shown on each of the &lt;30%/30-70%/&gt;70% presets.
+3. Select the "&lt;30% low" preset, tap Apply, check that every returned SKU falls within the displayed range.
+4. Switch to a different keyword (e.g. "beer", a very different price range), repeat steps 1-2, and confirm the 3 preset ranges change to match the new result set (not a fixed system-wide threshold).</t>
+        </is>
+      </c>
+      <c r="I151" s="35" t="inlineStr">
+        <is>
+          <t>"milk" vs "beer", the &lt;30% preset</t>
+        </is>
+      </c>
+      <c r="J151" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the 3 preset ranges must be computed dynamically from the CURRENT result set's price distribution (changing keyword -&gt; changing preset ranges), not a fixed threshold; every SKU returned when a preset is selected must fall within the displayed range. Not yet confirmed whether the basis is the original price or the post-discount price — see QnA-41.</t>
+        </is>
+      </c>
+      <c r="K151" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L151" s="28" t="n"/>
+      <c r="M151" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N151" s="28" t="n"/>
+      <c r="O151" s="28" t="n"/>
+      <c r="P151" s="35" t="inlineStr">
+        <is>
+          <t>QnA-41</t>
+        </is>
+      </c>
+      <c r="Q151" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-41: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC9-TC1</t>
+        </is>
+      </c>
+      <c r="B152" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC9</t>
+        </is>
+      </c>
+      <c r="C152" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D152" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E152" s="35" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="F152" s="35" t="inlineStr">
+        <is>
+          <t>Select "Standard delivery" — confirmed: exactly 1 checkbox in the tab</t>
+        </is>
+      </c>
+      <c r="G152" s="35" t="inlineStr">
+        <is>
+          <t>The Delivery tab has no active condition yet.</t>
+        </is>
+      </c>
+      <c r="H152" s="35" t="inlineStr">
+        <is>
+          <t>1. Open Filter, switch to the Delivery tab.
+2. Count and record every option shown in the tab (the BRD only states "Standard delivery").
+3. Select "Standard delivery", check the Delivery tab badge.
+4. Tap Apply, check the returned results.</t>
+        </is>
+      </c>
+      <c r="I152" s="35" t="inlineStr">
+        <is>
+          <t>Delivery tab</t>
+        </is>
+      </c>
+      <c r="J152" s="35" t="inlineStr">
+        <is>
+          <t>The Delivery tab has exactly 1 option: the "Standard delivery" checkbox (confirmed per the updated storyboard v0.1-20260819, component #6 "Delivery &amp; other groups") — not a multi-option list. The Delivery tab badge only has 2 states: 0 (unselected) or 1 (selected). Filtered results only include SKUs eligible for standard delivery.</t>
+        </is>
+      </c>
+      <c r="K152" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L152" s="28" t="n"/>
+      <c r="M152" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N152" s="28" t="n"/>
+      <c r="O152" s="28" t="n"/>
+      <c r="P152" s="35" t="inlineStr">
+        <is>
+          <t>QnA-42</t>
+        </is>
+      </c>
+      <c r="Q152" s="35" t="inlineStr">
+        <is>
+          <t>RESOLVED — QnA-42: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10-TC1</t>
+        </is>
+      </c>
+      <c r="B153" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10</t>
+        </is>
+      </c>
+      <c r="C153" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D153" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E153" s="27" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="F153" s="27" t="inlineStr">
+        <is>
+          <t>The list of 5 Rating levels matches the spec, single-select only</t>
+        </is>
+      </c>
+      <c r="G153" s="27" t="inlineStr">
+        <is>
+          <t>No Rating level selected yet.</t>
+        </is>
+      </c>
+      <c r="H153" s="27" t="inlineStr">
+        <is>
+          <t>1. Open Filter, switch to the Rating tab.
+2. Count and compare the 5 displayed level names against the BRD (5 stars / 4 stars &amp; up / 3 stars &amp; up / 2 stars &amp; up / 1 star &amp; up).
+3. Select "4 stars &amp; up", check the Rating tab badge.
+4. Select "3 stars &amp; up" next, without deselecting the previous one.</t>
+        </is>
+      </c>
+      <c r="I153" s="27" t="inlineStr">
+        <is>
+          <t>5 Rating levels</t>
+        </is>
+      </c>
+      <c r="J153" s="27" t="inlineStr">
+        <is>
+          <t>The list correctly shows 5 levels, in the correct order and naming per BRD FR-SF-04; selecting a second level ("3 stars &amp; up") automatically deselects the previous one ("4 stars &amp; up") — only 1 level active at a time (the Rating tab badge is always = 1 when something is selected, matching the single-select nature of the Category tab).</t>
+        </is>
+      </c>
+      <c r="K153" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L153" s="28" t="n"/>
+      <c r="M153" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N153" s="28" t="n"/>
+      <c r="O153" s="28" t="n"/>
+      <c r="P153" s="27" t="n"/>
+      <c r="Q153" s="27" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10-TC2</t>
+        </is>
+      </c>
+      <c r="B154" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10</t>
+        </is>
+      </c>
+      <c r="C154" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D154" s="27" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E154" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F154" s="27" t="inlineStr">
+        <is>
+          <t>Verify "N stars &amp; up" correctly returns the &gt;= N threshold (including N and above)</t>
+        </is>
+      </c>
+      <c r="G154" s="27" t="inlineStr">
+        <is>
+          <t>The result set has SKUs spread across ratings from 1 to 5 stars.</t>
+        </is>
+      </c>
+      <c r="H154" s="27" t="inlineStr">
+        <is>
+          <t>1. Open Filter, Rating tab, select "4 stars &amp; up".
+2. Tap Apply.
+3. Check the rating of every SKU in the returned results — confirm none has a rating &lt; 4.0.
+4. Check that a 5.0-rated SKU still appears in the results (not mistakenly excluded as if the filter meant "exactly 4 stars only").</t>
+        </is>
+      </c>
+      <c r="I154" s="27" t="inlineStr">
+        <is>
+          <t>"4 stars &amp; up"</t>
+        </is>
+      </c>
+      <c r="J154" s="27" t="inlineStr">
+        <is>
+          <t>100% of the SKUs in the results have rating &gt;= 4.0 (including 5-star SKUs); no SKU with rating &lt; 4.0 appears in the results.</t>
+        </is>
+      </c>
+      <c r="K154" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L154" s="28" t="n"/>
+      <c r="M154" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N154" s="28" t="n"/>
+      <c r="O154" s="28" t="n"/>
+      <c r="P154" s="27" t="n"/>
+      <c r="Q154" s="27" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-011-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B155" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-011-SC1</t>
+        </is>
+      </c>
+      <c r="C155" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-011</t>
+        </is>
+      </c>
+      <c r="D155" s="27" t="inlineStr">
+        <is>
+          <t>No clear FR ID in the BRD — see QnA-10</t>
+        </is>
+      </c>
+      <c r="E155" s="27" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F155" s="27" t="inlineStr">
+        <is>
+          <t>Tapping the confirmation Toast — no action occurs</t>
+        </is>
+      </c>
+      <c r="G155" s="27" t="inlineStr">
+        <is>
+          <t>The "Added to cart" Toast is showing after tapping (+).</t>
+        </is>
+      </c>
+      <c r="H155" s="27" t="inlineStr">
+        <is>
+          <t>1. Tap (+) on 1 Product Card, wait for the confirmation Toast to appear.
+2. While the Toast is still showing (before it auto-dismisses), tap directly on the body of the Toast (image/text area, not a close button if one exists).
+3. Check the UI immediately after the tap.
+4. Wait out the 3 seconds, confirm the Toast auto-dismisses normally as if nothing had happened.</t>
+        </is>
+      </c>
+      <c r="I155" s="27" t="inlineStr">
+        <is>
+          <t>Tap (+) -&gt; tap the Toast body</t>
+        </is>
+      </c>
+      <c r="J155" s="27" t="inlineStr">
+        <is>
+          <t>Tapping the Toast body triggers NO action whatsoever — does not open the Cart page, does not navigate to a PDP, does not dismiss the Toast earlier than 3 seconds, and has no other effect; the Toast keeps counting down and auto-dismisses on schedule (3 seconds) exactly as it would without the tap.</t>
+        </is>
+      </c>
+      <c r="K155" s="27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L155" s="28" t="n"/>
+      <c r="M155" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N155" s="28" t="n"/>
+      <c r="O155" s="28" t="n"/>
+      <c r="P155" s="27" t="n"/>
+      <c r="Q155" s="27" t="inlineStr">
+        <is>
+          <t>This assumes the current design where the Toast body itself is a passive display with no interactive CTA; if QnA-08 lands on changing the CTA to "View Cart" (adding an explicit button inside the Toast), a separate test case will be needed for tapping that CTA button — this TC only confirms that tapping the Toast BODY (outside any button, if one exists) has no unintended effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B156" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1</t>
+        </is>
+      </c>
+      <c r="C156" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D156" s="35" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07</t>
+        </is>
+      </c>
+      <c r="E156" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F156" s="35" t="inlineStr">
+        <is>
+          <t>Cross-sell (Basket Analysis) suggestions reflect real co-purchase data — TBD on the exact formula</t>
+        </is>
+      </c>
+      <c r="G156" s="35" t="inlineStr">
+        <is>
+          <t>Order history data clearly shows one pair of products that are frequently bought together (e.g. Corona beer + peanuts appearing together in orders at a high frequency).</t>
+        </is>
+      </c>
+      <c r="H156" s="35" t="inlineStr">
+        <is>
+          <t>1. Search a keyword that leads to Zero Result for an out-of-stock product with clear co-purchase data (e.g. "Corona beer", out of stock).
+2. Check the "You might like" block — confirm the known co-purchased product (e.g. peanuts) appears in the Cross-sell suggestions.
+3. Check whether a completely unrelated product (e.g. gardening tools) is mistakenly suggested.</t>
+        </is>
+      </c>
+      <c r="I156" s="35" t="inlineStr">
+        <is>
+          <t>"Corona beer" (out of stock, has co-purchase data with peanuts)</t>
+        </is>
+      </c>
+      <c r="J156" s="35" t="inlineStr">
+        <is>
+          <t>TBD — minimum requirement: the known co-purchased product (peanuts) must appear in the Cross-sell suggestions; a completely unrelated product must not be suggested. The exact formula (support/confidence threshold, personalized vs. aggregated, data time window) has not been confirmed — cannot be scored against precise details until an official formula is provided. See QnA-45.</t>
+        </is>
+      </c>
+      <c r="K156" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L156" s="28" t="n"/>
+      <c r="M156" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N156" s="28" t="n"/>
+      <c r="O156" s="28" t="n"/>
+      <c r="P156" s="35" t="inlineStr">
+        <is>
+          <t>QnA-45</t>
+        </is>
+      </c>
+      <c r="Q156" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-45: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B157" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1</t>
+        </is>
+      </c>
+      <c r="C157" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D157" s="35" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07</t>
+        </is>
+      </c>
+      <c r="E157" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F157" s="35" t="inlineStr">
+        <is>
+          <t>Maximum number of products in the "You might like" block when scrolling to load more — TBD</t>
+        </is>
+      </c>
+      <c r="G157" s="35" t="inlineStr">
+        <is>
+          <t>On the Zero Result Page with the suggestion block showing the default 10 products (Best-seller fallback, a list long enough to test lazy-loading multiple times).</t>
+        </is>
+      </c>
+      <c r="H157" s="35" t="inlineStr">
+        <is>
+          <t>1. Enter the Zero Result Page, confirm the first 10 products are shown by default.
+2. Scroll to the end of the list, wait for lazy-loading to fetch more.
+3. Repeat scrolling several times, counting the total number of products loaded until loading stops or a clear limit is reached.</t>
+        </is>
+      </c>
+      <c r="I157" s="35" t="inlineStr">
+        <is>
+          <t>Repeatedly scroll the "You might like" block</t>
+        </is>
+      </c>
+      <c r="J157" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the BRD only confirms a default of 10 products (Lazy Loading), without specifying a maximum cap (stopping at a specific threshold, or loading until the Best-seller data is exhausted). Cannot be scored against a precise quantitative maximum until officially confirmed. See QnA-46.</t>
+        </is>
+      </c>
+      <c r="K157" s="35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L157" s="28" t="n"/>
+      <c r="M157" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N157" s="28" t="n"/>
+      <c r="O157" s="28" t="n"/>
+      <c r="P157" s="35" t="inlineStr">
+        <is>
+          <t>QnA-46</t>
+        </is>
+      </c>
+      <c r="Q157" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-46: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B158" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4</t>
+        </is>
+      </c>
+      <c r="C158" s="27" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D158" s="27" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07, FR-PR-01 -&gt; FR-PR-05</t>
+        </is>
+      </c>
+      <c r="E158" s="27" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F158" s="27" t="inlineStr">
+        <is>
+          <t>Keyword exactly matches 1 out-of-stock SKU but another matching SKU is in stock — stays on SS-SCR-005, Zero Result is not triggered</t>
+        </is>
+      </c>
+      <c r="G158" s="27" t="inlineStr">
+        <is>
+          <t>The catalogue has &gt;=2 SKUs that both directly match 1 keyword, where 1 SKU has stock=0 and &gt;=1 SKU is in stock.</t>
+        </is>
+      </c>
+      <c r="H158" s="27" t="inlineStr">
+        <is>
+          <t>1. Set up data: keyword "X" directly matches SKU-A (out of stock) and SKU-B (in stock).
+2. Search "X".
+3. Check which screen is returned (SS-SCR-005 or SS-SCR-012).
+4. If SS-SCR-005, check SKU-A's position in the results list.</t>
+        </is>
+      </c>
+      <c r="I158" s="27" t="inlineStr">
+        <is>
+          <t>Keyword "X" -&gt; SKU-A (out of stock) + SKU-B (in stock)</t>
+        </is>
+      </c>
+      <c r="J158" s="27" t="inlineStr">
+        <is>
+          <t>The system returns the SS-SCR-005 results page (does NOT switch to the Zero Result Page); SKU-A (out of stock) still appears in the list but is pushed to the very bottom (below every in-stock SKU, even ones with a lower relevance score) per the Out-of-stock override rule; the "You might like" block does not appear since this is not a Zero Result flow.</t>
+        </is>
+      </c>
+      <c r="K158" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L158" s="28" t="n"/>
+      <c r="M158" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N158" s="28" t="n"/>
+      <c r="O158" s="28" t="n"/>
+      <c r="P158" s="27" t="n"/>
+      <c r="Q158" s="27" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B159" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4</t>
+        </is>
+      </c>
+      <c r="C159" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D159" s="35" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07, FR-PR-01 -&gt; FR-PR-05</t>
+        </is>
+      </c>
+      <c r="E159" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F159" s="35" t="inlineStr">
+        <is>
+          <t>Every SKU that directly matches the keyword is out of stock — TBD whether Zero Result is triggered</t>
+        </is>
+      </c>
+      <c r="G159" s="35" t="inlineStr">
+        <is>
+          <t>The catalogue has SKUs directly matching a keyword, but ALL of them have stock=0 (no in-stock direct match remains).</t>
+        </is>
+      </c>
+      <c r="H159" s="35" t="inlineStr">
+        <is>
+          <t>1. Set up data: keyword "Y" only directly matches SKU-C, and SKU-C has stock=0 (no other SKU directly matches).
+2. Search "Y".
+3. Check which screen is returned: SS-SCR-005 (showing the out-of-stock SKU-C alone in the list) or SS-SCR-012 (Zero Result, with the "You might like" block)?</t>
+        </is>
+      </c>
+      <c r="I159" s="35" t="inlineStr">
+        <is>
+          <t>Keyword "Y" -&gt; only matches SKU-C (out of stock)</t>
+        </is>
+      </c>
+      <c r="J159" s="35" t="inlineStr">
+        <is>
+          <t>TBD — not yet confirmed whether the system treats this as (a) still having 1 matching result (even out of stock) and stays on SS-SCR-005, or (b) treats it as "0 purchasable results" and switches to the Zero Result Page flow (SS-SCR-012) with the Substitute/Cross-sell/Best-seller suggestion block. Cannot be scored Pass/Fail until confirmed. See QnA-44.</t>
+        </is>
+      </c>
+      <c r="K159" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L159" s="28" t="n"/>
+      <c r="M159" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N159" s="28" t="n"/>
+      <c r="O159" s="28" t="n"/>
+      <c r="P159" s="35" t="inlineStr">
+        <is>
+          <t>QnA-44</t>
+        </is>
+      </c>
+      <c r="Q159" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-44: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-010-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B160" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-010-SC4</t>
+        </is>
+      </c>
+      <c r="C160" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-010</t>
+        </is>
+      </c>
+      <c r="D160" s="35" t="inlineStr">
+        <is>
+          <t>FR-SF-03</t>
+        </is>
+      </c>
+      <c r="E160" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F160" s="35" t="inlineStr">
+        <is>
+          <t>Searching a new keyword automatically clears the old keyword's filter</t>
+        </is>
+      </c>
+      <c r="G160" s="35" t="inlineStr">
+        <is>
+          <t>On the "milk" results with the "Sugar-free" filter active (badge=1).</t>
+        </is>
+      </c>
+      <c r="H160" s="35" t="inlineStr">
+        <is>
+          <t>1. On the "milk" results page, apply the "Sugar-free" filter.
+2. Tap the Search Bar, clear "milk", type a completely different keyword "beer", submit the search.
+3. Check the "beer" results page — check the Filter button badge and whether any filter chip is active.</t>
+        </is>
+      </c>
+      <c r="I160" s="35" t="inlineStr">
+        <is>
+          <t>"milk" (filter=Sugar-free) -&gt; search new keyword "beer"</t>
+        </is>
+      </c>
+      <c r="J160" s="35" t="inlineStr">
+        <is>
+          <t>The "beer" results page no longer has the "Sugar-free" filter active; the Filter button badge resets to 0/hidden — the filter was automatically cleared when switching to a completely new keyword, per the updated storyboard (see QnA-06, now Resolved). Note: this behavior applies to SEARCHING A NEW KEYWORD via the Search Bar — it does not necessarily apply to directly EDITING the existing keyword in place on the results page's Search Bar (if that is a separate flow, the two UX paths need to be clearly distinguished).</t>
+        </is>
+      </c>
+      <c r="K160" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L160" s="28" t="n"/>
+      <c r="M160" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N160" s="28" t="n"/>
+      <c r="O160" s="28" t="n"/>
+      <c r="P160" s="35" t="inlineStr">
+        <is>
+          <t>QnA-06</t>
+        </is>
+      </c>
+      <c r="Q160" s="35" t="inlineStr">
+        <is>
+          <t>RESOLVED — QnA-06: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-013-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B161" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-013-SC1</t>
+        </is>
+      </c>
+      <c r="C161" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-013</t>
+        </is>
+      </c>
+      <c r="D161" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-01</t>
+        </is>
+      </c>
+      <c r="E161" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F161" s="35" t="inlineStr">
+        <is>
+          <t>The "Rear camera"/"Front camera" badge matches the active camera; the Flip button updates both the badge and the actual camera source</t>
+        </is>
+      </c>
+      <c r="G161" s="35" t="inlineStr">
+        <is>
+          <t>On the Camera Screen, default camera = "Rear camera".</t>
+        </is>
+      </c>
+      <c r="H161" s="35" t="inlineStr">
+        <is>
+          <t>1. Open the Camera Screen, check the badge in the middle of the header shows "Rear camera".
+2. Tap the "Flip" button (bottom-right corner).
+3. Check whether the badge changes to "Front camera", and whether the viewfinder genuinely switches to the front (selfie) camera.
+4. Tap "Flip" again, confirm it returns to "Rear camera" with the rear-camera viewfinder.</t>
+        </is>
+      </c>
+      <c r="I161" s="35" t="inlineStr">
+        <is>
+          <t>Tap "Flip" twice in a row</t>
+        </is>
+      </c>
+      <c r="J161" s="35" t="inlineStr">
+        <is>
+          <t>The badge and the viewfinder are ALWAYS in sync at every moment — never a case where the badge reads "Front camera" while the viewfinder still shows the rear camera feed (or vice versa); each tap of "Flip" updates both immediately, with no lag that could desync the state.</t>
+        </is>
+      </c>
+      <c r="K161" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L161" s="28" t="n"/>
+      <c r="M161" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N161" s="28" t="n"/>
+      <c r="O161" s="28" t="n"/>
+      <c r="P161" s="35" t="n"/>
+      <c r="Q161" s="35" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-013-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B162" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-013-SC1</t>
+        </is>
+      </c>
+      <c r="C162" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-013</t>
+        </is>
+      </c>
+      <c r="D162" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-01</t>
+        </is>
+      </c>
+      <c r="E162" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F162" s="35" t="inlineStr">
+        <is>
+          <t>Capturing right after flipping the camera — the photo must come from the new camera, no race condition</t>
+        </is>
+      </c>
+      <c r="G162" s="35" t="inlineStr">
+        <is>
+          <t>On the Camera Screen with "Rear camera" active.</t>
+        </is>
+      </c>
+      <c r="H162" s="35" t="inlineStr">
+        <is>
+          <t>1. Tap "Flip" to switch to "Front camera".
+2. IMMEDIATELY (no wait) tap the "Capture" button.
+3. Check whether the resulting photo genuinely came from the front camera (selfie framing) or accidentally still came from the rear camera (a race condition where the camera hadn't finished initializing).
+4. Repeat steps 1-3 several times (Flip then Capture back-to-back, no pause) to check stability.</t>
+        </is>
+      </c>
+      <c r="I162" s="35" t="inlineStr">
+        <is>
+          <t>Flip -&gt; Capture immediately (repeated)</t>
+        </is>
+      </c>
+      <c r="J162" s="35" t="inlineStr">
+        <is>
+          <t>The captured photo always matches whichever camera was active at the moment Capture was tapped (never accidentally captures from the stale camera); no crash or freeze under rapid flip+capture spamming.</t>
+        </is>
+      </c>
+      <c r="K162" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L162" s="28" t="n"/>
+      <c r="M162" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N162" s="28" t="n"/>
+      <c r="O162" s="28" t="n"/>
+      <c r="P162" s="35" t="n"/>
+      <c r="Q162" s="35" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B163" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC1</t>
+        </is>
+      </c>
+      <c r="C163" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D163" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="E163" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F163" s="35" t="inlineStr">
+        <is>
+          <t>PNG format is accepted and processed correctly</t>
+        </is>
+      </c>
+      <c r="G163" s="35" t="inlineStr">
+        <is>
+          <t>Library access is granted; a valid PNG photo exists in the tray.</t>
+        </is>
+      </c>
+      <c r="H163" s="35" t="inlineStr">
+        <is>
+          <t>1. Open the Gallery tray.
+2. Select 1 PNG-format photo (valid size, e.g. 2MB).
+3. Check whether the system accepts it and switches to the Loading Screen.</t>
+        </is>
+      </c>
+      <c r="I163" s="35" t="inlineStr">
+        <is>
+          <t>PNG photo, 2MB</t>
+        </is>
+      </c>
+      <c r="J163" s="35" t="inlineStr">
+        <is>
+          <t>The PNG photo is accepted, no error Toast shown, switches straight to the Loading Screen (SS-SCR-004) — per FR-IS-04 (accepts JPG/PNG/WEBP).</t>
+        </is>
+      </c>
+      <c r="K163" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L163" s="28" t="n"/>
+      <c r="M163" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N163" s="28" t="n"/>
+      <c r="O163" s="28" t="n"/>
+      <c r="P163" s="35" t="n"/>
+      <c r="Q163" s="35" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B164" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC1</t>
+        </is>
+      </c>
+      <c r="C164" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D164" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="E164" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F164" s="35" t="inlineStr">
+        <is>
+          <t>WEBP format is accepted — no test case covered this format before this update</t>
+        </is>
+      </c>
+      <c r="G164" s="35" t="inlineStr">
+        <is>
+          <t>Library access is granted; a valid WEBP photo exists in the tray.</t>
+        </is>
+      </c>
+      <c r="H164" s="35" t="inlineStr">
+        <is>
+          <t>1. Open the Gallery tray.
+2. Select 1 WEBP-format photo (valid size, e.g. 2MB).
+3. Check whether the system accepts it and switches to the Loading Screen.</t>
+        </is>
+      </c>
+      <c r="I164" s="35" t="inlineStr">
+        <is>
+          <t>WEBP photo, 2MB</t>
+        </is>
+      </c>
+      <c r="J164" s="35" t="inlineStr">
+        <is>
+          <t>The WEBP photo is accepted, no error Toast shown, switches straight to the Loading Screen (SS-SCR-004) — per FR-IS-04 (accepts JPG/PNG/WEBP). This is the only format in the BRD's list that had never been individually tested before this update.</t>
+        </is>
+      </c>
+      <c r="K164" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L164" s="28" t="n"/>
+      <c r="M164" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N164" s="28" t="n"/>
+      <c r="O164" s="28" t="n"/>
+      <c r="P164" s="35" t="n"/>
+      <c r="Q164" s="35" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B165" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4</t>
+        </is>
+      </c>
+      <c r="C165" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D165" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="E165" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F165" s="35" t="inlineStr">
+        <is>
+          <t>Tapping the "X" button in the Gallery tray header closes it back to the Camera Screen, no photo selected</t>
+        </is>
+      </c>
+      <c r="G165" s="35" t="inlineStr">
+        <is>
+          <t>The "Recent Photos" tray is open.</t>
+        </is>
+      </c>
+      <c r="H165" s="35" t="inlineStr">
+        <is>
+          <t>1. Open the Gallery tray from the Camera Screen.
+2. Tap the "X" button in the top-right corner of the tray header.
+3. Check the screen after it closes.</t>
+        </is>
+      </c>
+      <c r="I165" s="35" t="inlineStr">
+        <is>
+          <t>Tap "X"</t>
+        </is>
+      </c>
+      <c r="J165" s="35" t="inlineStr">
+        <is>
+          <t>Returns to the correct Camera Screen (no photo selected); the camera is still running in the background exactly as it was before the tray opened (not restarted from scratch).</t>
+        </is>
+      </c>
+      <c r="K165" s="35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L165" s="28" t="n"/>
+      <c r="M165" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N165" s="28" t="n"/>
+      <c r="O165" s="28" t="n"/>
+      <c r="P165" s="35" t="n"/>
+      <c r="Q165" s="35" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B166" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4</t>
+        </is>
+      </c>
+      <c r="C166" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D166" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="E166" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F166" s="35" t="inlineStr">
+        <is>
+          <t>Tapping the dimmed area outside the Gallery tray also closes it, consistent with the X button</t>
+        </is>
+      </c>
+      <c r="G166" s="35" t="inlineStr">
+        <is>
+          <t>The "Recent Photos" tray is open.</t>
+        </is>
+      </c>
+      <c r="H166" s="35" t="inlineStr">
+        <is>
+          <t>1. Open the Gallery tray from the Camera Screen.
+2. Tap the camera preview area above the tray (the dimmed area outside the sheet, not tapping any photo in the grid).
+3. Check the screen after the tap.</t>
+        </is>
+      </c>
+      <c r="I166" s="35" t="inlineStr">
+        <is>
+          <t>Tap outside the sheet</t>
+        </is>
+      </c>
+      <c r="J166" s="35" t="inlineStr">
+        <is>
+          <t>The tray closes, returning to the Camera Screen exactly like the "X" button behavior (TC1) — no photo selected, no behavioral difference between the two dismissal methods.</t>
+        </is>
+      </c>
+      <c r="K166" s="35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L166" s="28" t="n"/>
+      <c r="M166" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N166" s="28" t="n"/>
+      <c r="O166" s="28" t="n"/>
+      <c r="P166" s="35" t="n"/>
+      <c r="Q166" s="35" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-015-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B167" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-015-SC1</t>
+        </is>
+      </c>
+      <c r="C167" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-015</t>
+        </is>
+      </c>
+      <c r="D167" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-03, FR-IS-07</t>
+        </is>
+      </c>
+      <c r="E167" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F167" s="35" t="inlineStr">
+        <is>
+          <t>Capturing/selecting a new photo while already on the image results page — the new photo fully overrides the old one</t>
+        </is>
+      </c>
+      <c r="G167" s="35" t="inlineStr">
+        <is>
+          <t>On the image results page (SS-SCR-015) with photo A (TH True Milk carton) already processed.</t>
+        </is>
+      </c>
+      <c r="H167" s="35" t="inlineStr">
+        <is>
+          <t>1. From the current results page (photo A: TH True Milk carton), tap the Camera icon on the Search Bar to reopen the Camera Screen.
+2. Capture a COMPLETELY DIFFERENT photo (photo B: Vinamilk carton).
+3. Wait for processing to finish, check the new results page.
+4. Check the Search Bar thumbnail, the product list, and the Sort/Filter state to confirm they fully belong to photo B, with nothing left over from photo A.</t>
+        </is>
+      </c>
+      <c r="I167" s="35" t="inlineStr">
+        <is>
+          <t>Photo A (TH True Milk) -&gt; capture photo B (Vinamilk)</t>
+        </is>
+      </c>
+      <c r="J167" s="35" t="inlineStr">
+        <is>
+          <t>Photo B fully overrides photo A: the Search Bar thumbnail changes to photo B; the result list belongs to photo B (no products only relevant to photo A remain); any filter/sort applied for photo A resets to default for the new query (similar to the confirmed new-keyword behavior in SS-SCR-010-SC4).</t>
+        </is>
+      </c>
+      <c r="K167" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L167" s="28" t="n"/>
+      <c r="M167" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N167" s="28" t="n"/>
+      <c r="O167" s="28" t="n"/>
+      <c r="P167" s="35" t="n"/>
+      <c r="Q167" s="35" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-015-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B168" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-015-SC1</t>
+        </is>
+      </c>
+      <c r="C168" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-015</t>
+        </is>
+      </c>
+      <c r="D168" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-03, FR-IS-07</t>
+        </is>
+      </c>
+      <c r="E168" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F168" s="35" t="inlineStr">
+        <is>
+          <t>After a successful capture or gallery selection, the photo correctly loads into the Search Bar on the results page</t>
+        </is>
+      </c>
+      <c r="G168" s="35" t="inlineStr">
+        <is>
+          <t>One image-search round has just been processed.</t>
+        </is>
+      </c>
+      <c r="H168" s="35" t="inlineStr">
+        <is>
+          <t>1. Capture a photo directly (SS-SCR-013) successfully, check the Search Bar on the results page (SS-SCR-015).
+2. Repeat, but this time SELECT a photo from the gallery (SS-SCR-014) instead of capturing directly, check the Search Bar.</t>
+        </is>
+      </c>
+      <c r="I168" s="35" t="inlineStr">
+        <is>
+          <t>Capture flow / Gallery-selection flow</t>
+        </is>
+      </c>
+      <c r="J168" s="35" t="inlineStr">
+        <is>
+          <t>In BOTH flows, the just-processed photo (captured directly or selected from the gallery) correctly appears as a small thumbnail INSIDE the Search Bar (replacing the text-keyword position), with no difference in thumbnail display behavior between the two input sources.</t>
+        </is>
+      </c>
+      <c r="K168" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L168" s="28" t="n"/>
+      <c r="M168" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N168" s="28" t="n"/>
+      <c r="O168" s="28" t="n"/>
+      <c r="P168" s="35" t="n"/>
+      <c r="Q168" s="35" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-016-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B169" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-016-SC1</t>
+        </is>
+      </c>
+      <c r="C169" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-016</t>
+        </is>
+      </c>
+      <c r="D169" s="35" t="inlineStr">
+        <is>
+          <t>FR-IS-05</t>
+        </is>
+      </c>
+      <c r="E169" s="35" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F169" s="35" t="inlineStr">
+        <is>
+          <t>Tapping the header "Back" button on the "Not recognized" failure screen — destination TBD</t>
+        </is>
+      </c>
+      <c r="G169" s="35" t="inlineStr">
+        <is>
+          <t>On the "Not recognized" failure screen (SS-SCR-016) after uploading a blurry photo.</t>
+        </is>
+      </c>
+      <c r="H169" s="35" t="inlineStr">
+        <is>
+          <t>1. Upload a blurry photo, confirm the "Not recognized" failure screen appears.
+2. Tap the "Back" button in the top-left corner of the header (not "Retry" or "Search by keyword").
+3. Check which screen it navigates to.</t>
+        </is>
+      </c>
+      <c r="I169" s="35" t="inlineStr">
+        <is>
+          <t>Tap "Back" in the header</t>
+        </is>
+      </c>
+      <c r="J169" s="35" t="inlineStr">
+        <is>
+          <t>TBD — not yet confirmed whether Back behaves identically to "Retry" (returns to the Camera Screen) or differently (exits the image-search flow entirely, back to whatever screen opened it, e.g. Pre-search or the previous results page). Minimum requirement: no crash, does not get stuck on the failure screen. Cannot be scored Pass/Fail until confirmed. See QnA-50.</t>
+        </is>
+      </c>
+      <c r="K169" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L169" s="28" t="n"/>
+      <c r="M169" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N169" s="28" t="n"/>
+      <c r="O169" s="28" t="n"/>
+      <c r="P169" s="35" t="inlineStr">
+        <is>
+          <t>QnA-50</t>
+        </is>
+      </c>
+      <c r="Q169" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-50: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B170" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC1</t>
+        </is>
+      </c>
+      <c r="C170" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-018</t>
+        </is>
+      </c>
+      <c r="D170" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-04, FR-VS-05</t>
+        </is>
+      </c>
+      <c r="E170" s="35" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F170" s="35" t="inlineStr">
+        <is>
+          <t>A valid transcript that matches no product (nonsense to the catalogue) correctly falls through to Zero Result, same as the Text flow</t>
+        </is>
+      </c>
+      <c r="G170" s="35" t="inlineStr">
+        <is>
+          <t>Voice-to-text processing is done, the transcript is valid (not empty) but matches nothing in the catalogue.</t>
+        </is>
+      </c>
+      <c r="H170" s="35" t="inlineStr">
+        <is>
+          <t>1. Say a clearly-spoken sentence that is not a valid product name (e.g. "Tesla mosquito spray").
+2. Let the system transcribe it successfully (does not fall into the voice-recognition-failure flow, SS-SCR-019).
+3. Check which page it navigates to.</t>
+        </is>
+      </c>
+      <c r="I170" s="35" t="inlineStr">
+        <is>
+          <t>"Tesla mosquito spray" (spoken)</t>
+        </is>
+      </c>
+      <c r="J170" s="35" t="inlineStr">
+        <is>
+          <t>Since the transcript is valid and not empty, the system does NOT switch to the voice failure screen (SS-SCR-019, reserved for unclear speech/empty transcript — see SC2). Since the catalogue has no matching SKU, the system correctly applies the same 3-tier Zero Result Prevention mechanism as Text Search: shows the "No results found" page (SS-SCR-012) with the "You might like" block, not a blank page or a voice error.</t>
+        </is>
+      </c>
+      <c r="K170" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L170" s="28" t="n"/>
+      <c r="M170" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N170" s="28" t="n"/>
+      <c r="O170" s="28" t="n"/>
+      <c r="P170" s="35" t="n"/>
+      <c r="Q170" s="35" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-019-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B171" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-019-SC1</t>
+        </is>
+      </c>
+      <c r="C171" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-019</t>
+        </is>
+      </c>
+      <c r="D171" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-06</t>
+        </is>
+      </c>
+      <c r="E171" s="35" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F171" s="35" t="inlineStr">
+        <is>
+          <t>Tapping the header "Back" button on the voice "Not recognized" failure screen — destination TBD</t>
+        </is>
+      </c>
+      <c r="G171" s="35" t="inlineStr">
+        <is>
+          <t>On the "Not recognized" failure screen (SS-SCR-019) after an unclear recording.</t>
+        </is>
+      </c>
+      <c r="H171" s="35" t="inlineStr">
+        <is>
+          <t>1. Record with background noise/silence, confirm the "Not recognized" failure screen appears.
+2. Tap the "Back" button in the top-left corner of the header (not "Retry" or "Search by keyword").
+3. Check which screen it navigates to.</t>
+        </is>
+      </c>
+      <c r="I171" s="35" t="inlineStr">
+        <is>
+          <t>Tap "Back" in the header</t>
+        </is>
+      </c>
+      <c r="J171" s="35" t="inlineStr">
+        <is>
+          <t>TBD — not yet confirmed whether Back behaves identically to "Retry" (reopens the recording layer) or differently (exits the voice-search flow entirely, back to whatever screen opened it, e.g. Pre-search or the previous results page) — the same open question as SS-SCR-016-SC1-TC3 (image flow). Minimum requirement: no crash, does not get stuck on the failure screen. Cannot be scored Pass/Fail until confirmed. See QnA-50.</t>
+        </is>
+      </c>
+      <c r="K171" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L171" s="28" t="n"/>
+      <c r="M171" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N171" s="28" t="n"/>
+      <c r="O171" s="28" t="n"/>
+      <c r="P171" s="35" t="inlineStr">
+        <is>
+          <t>QnA-50</t>
+        </is>
+      </c>
+      <c r="Q171" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-50: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B172" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C172" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D172" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E172" s="35" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F172" s="35" t="inlineStr">
+        <is>
+          <t>Speaking in English — the system correctly auto-detects the language and transcribes accurately</t>
+        </is>
+      </c>
+      <c r="G172" s="35" t="inlineStr">
+        <is>
+          <t>Mic permission is granted; the system UI is in Vietnamese (app language unchanged).</t>
+        </is>
+      </c>
+      <c r="H172" s="35" t="inlineStr">
+        <is>
+          <t>1. Tap the Mic icon, start recording.
+2. Speak a clear English sentence (e.g. "fresh milk one liter").
+3. End the recording, check the recognized text and the returned results.</t>
+        </is>
+      </c>
+      <c r="I172" s="35" t="inlineStr">
+        <is>
+          <t>"fresh milk one liter" (English)</t>
+        </is>
+      </c>
+      <c r="J172" s="35" t="inlineStr">
+        <is>
+          <t>The system automatically detects this as English WITHOUT requiring the customer to manually select a language beforehand; the transcript correctly shows the English sentence spoken; the search results return relevant fresh-milk products (applying the multilingual logic in FR-SM-02 to map onto the Vietnamese catalogue).</t>
+        </is>
+      </c>
+      <c r="K172" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L172" s="28" t="n"/>
+      <c r="M172" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N172" s="28" t="n"/>
+      <c r="O172" s="28" t="n"/>
+      <c r="P172" s="35" t="n"/>
+      <c r="Q172" s="35" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B173" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C173" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D173" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E173" s="35" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F173" s="35" t="inlineStr">
+        <is>
+          <t>Speaking in Korean — the system correctly auto-detects the language and transcribes accurately</t>
+        </is>
+      </c>
+      <c r="G173" s="35" t="inlineStr">
+        <is>
+          <t>Mic permission is granted; the system UI is in Vietnamese.</t>
+        </is>
+      </c>
+      <c r="H173" s="35" t="inlineStr">
+        <is>
+          <t>1. Tap the Mic icon, start recording.
+2. Speak a clear Korean sentence (a common product name, e.g. the equivalent of "fresh milk").
+3. End the recording, check the recognized text and the returned results.</t>
+        </is>
+      </c>
+      <c r="I173" s="35" t="inlineStr">
+        <is>
+          <t>A Korean sentence (equivalent to "fresh milk")</t>
+        </is>
+      </c>
+      <c r="J173" s="35" t="inlineStr">
+        <is>
+          <t>The system automatically detects this as Korean without requiring manual selection; the transcript is correct; the search results return relevant products.</t>
+        </is>
+      </c>
+      <c r="K173" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L173" s="28" t="n"/>
+      <c r="M173" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N173" s="28" t="n"/>
+      <c r="O173" s="28" t="n"/>
+      <c r="P173" s="35" t="n"/>
+      <c r="Q173" s="35" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="B174" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C174" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D174" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E174" s="35" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F174" s="35" t="inlineStr">
+        <is>
+          <t>Speaking in Chinese — the system correctly auto-detects the language and transcribes accurately</t>
+        </is>
+      </c>
+      <c r="G174" s="35" t="inlineStr">
+        <is>
+          <t>Mic permission is granted; the system UI is in Vietnamese.</t>
+        </is>
+      </c>
+      <c r="H174" s="35" t="inlineStr">
+        <is>
+          <t>1. Tap the Mic icon, start recording.
+2. Speak a clear Chinese sentence (a common product name, e.g. the equivalent of "fresh milk").
+3. End the recording, check the recognized text and the returned results.</t>
+        </is>
+      </c>
+      <c r="I174" s="35" t="inlineStr">
+        <is>
+          <t>A Chinese sentence (equivalent to "fresh milk")</t>
+        </is>
+      </c>
+      <c r="J174" s="35" t="inlineStr">
+        <is>
+          <t>The system automatically detects this as Chinese without requiring manual selection; the transcript is correct; the search results return relevant products.</t>
+        </is>
+      </c>
+      <c r="K174" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L174" s="28" t="n"/>
+      <c r="M174" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N174" s="28" t="n"/>
+      <c r="O174" s="28" t="n"/>
+      <c r="P174" s="35" t="n"/>
+      <c r="Q174" s="35" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC4</t>
+        </is>
+      </c>
+      <c r="B175" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C175" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D175" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E175" s="35" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F175" s="35" t="inlineStr">
+        <is>
+          <t>Speaking in Russian — the system correctly auto-detects the language and transcribes accurately</t>
+        </is>
+      </c>
+      <c r="G175" s="35" t="inlineStr">
+        <is>
+          <t>Mic permission is granted; the system UI is in Vietnamese.</t>
+        </is>
+      </c>
+      <c r="H175" s="35" t="inlineStr">
+        <is>
+          <t>1. Tap the Mic icon, start recording.
+2. Speak a clear Russian sentence (a common product name, e.g. the equivalent of "fresh milk").
+3. End the recording, check the recognized text and the returned results.</t>
+        </is>
+      </c>
+      <c r="I175" s="35" t="inlineStr">
+        <is>
+          <t>A Russian sentence (equivalent to "fresh milk")</t>
+        </is>
+      </c>
+      <c r="J175" s="35" t="inlineStr">
+        <is>
+          <t>The system automatically detects this as Russian without requiring manual selection; the transcript is correct; the search results return relevant products.</t>
+        </is>
+      </c>
+      <c r="K175" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L175" s="28" t="n"/>
+      <c r="M175" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N175" s="28" t="n"/>
+      <c r="O175" s="28" t="n"/>
+      <c r="P175" s="35" t="n"/>
+      <c r="Q175" s="35" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC5</t>
+        </is>
+      </c>
+      <c r="B176" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C176" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D176" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E176" s="35" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F176" s="35" t="inlineStr">
+        <is>
+          <t>Switching spoken language between consecutive turns — the system does not get "stuck" on the previous language</t>
+        </is>
+      </c>
+      <c r="G176" s="35" t="inlineStr">
+        <is>
+          <t>Mic permission is granted.</t>
+        </is>
+      </c>
+      <c r="H176" s="35" t="inlineStr">
+        <is>
+          <t>1. Turn 1: speak in Vietnamese ("sữa tươi"), confirm the result is correct.
+2. Immediately next turn: speak in English ("fresh milk"), check whether the system correctly auto-detects the NEW language or still tries to interpret it as Vietnamese from the previous turn.
+3. Repeat, switching to Korean on the 3rd turn.</t>
+        </is>
+      </c>
+      <c r="I176" s="35" t="inlineStr">
+        <is>
+          <t>VI -&gt; EN -&gt; KR (3 consecutive turns)</t>
+        </is>
+      </c>
+      <c r="J176" s="35" t="inlineStr">
+        <is>
+          <t>Each recording turn has its language detected INDEPENDENTLY, unaffected by the language spoken in the immediately preceding turn; all 3 turns are transcribed correctly in their respective languages.</t>
+        </is>
+      </c>
+      <c r="K176" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L176" s="28" t="n"/>
+      <c r="M176" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N176" s="28" t="n"/>
+      <c r="O176" s="28" t="n"/>
+      <c r="P176" s="35" t="n"/>
+      <c r="Q176" s="35" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC3-TC1</t>
+        </is>
+      </c>
+      <c r="B177" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC3</t>
+        </is>
+      </c>
+      <c r="C177" s="35" t="inlineStr">
+        <is>
+          <t>SS-SCR-018</t>
+        </is>
+      </c>
+      <c r="D177" s="35" t="inlineStr">
+        <is>
+          <t>FR-VS-08, NFR-005</t>
+        </is>
+      </c>
+      <c r="E177" s="35" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F177" s="35" t="inlineStr">
+        <is>
+          <t>p95 voice search response time — measured for real, not yet scored Pass/Fail due to the conflicting thresholds (FR-VS-08 vs NFR-005)</t>
+        </is>
+      </c>
+      <c r="G177" s="35" t="inlineStr">
+        <is>
+          <t>Normal network conditions.</t>
+        </is>
+      </c>
+      <c r="H177" s="35" t="inlineStr">
+        <is>
+          <t>1. Perform 30+ voice searches with standard speech, under normal network conditions.
+2. Measure the time from the end of recording (auto-stop or manual stop) to the first product displaying on the results page, for each run (including the speech-to-text conversion time, per the measurement scope of FR-VS-08/NFR-005).
+3. Compute the p95 of the data set.</t>
+        </is>
+      </c>
+      <c r="I177" s="35" t="inlineStr">
+        <is>
+          <t>Standard speech x &gt;=30 runs</t>
+        </is>
+      </c>
+      <c r="J177" s="35" t="inlineStr">
+        <is>
+          <t>TBD — measures the actual p95, but does NOT score Pass/Fail until the official threshold is confirmed as 4,000ms (NFR-005) or 6,000ms (FR-VS-08). See QnA-30.</t>
+        </is>
+      </c>
+      <c r="K177" s="35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L177" s="28" t="n"/>
+      <c r="M177" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N177" s="28" t="n"/>
+      <c r="O177" s="28" t="n"/>
+      <c r="P177" s="35" t="inlineStr">
+        <is>
+          <t>QnA-30</t>
+        </is>
+      </c>
+      <c r="Q177" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-30: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13313,7 +18859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="16" min="1" max="1"/>
@@ -14376,6 +19922,110 @@
       <c r="M22" s="28" t="n"/>
       <c r="N22" s="27" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>INT-13-SC2</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Performance &amp; Scalability (NFR)</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>FR-GD-03, NFR-009</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>Behavior</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="inlineStr">
+        <is>
+          <t>When the AI Search (semantic) system fails or times out, the system automatically degrades (Graceful Degradation) to the basic keyword search algorithm, showing no technical error to the customer.</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>AI Search Service, Basic Keyword Search Engine (fallback), API Gateway</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="inlineStr">
+        <is>
+          <t>The test environment can simulate the AI Search Service being down/timing out (chaos testing or a feature flag disabling the AI service).</t>
+        </is>
+      </c>
+      <c r="I23" s="27" t="inlineStr">
+        <is>
+          <t>When the AI Search Service is unavailable, search requests automatically switch to the basic keyword algorithm; the customer still receives a reasonable results page (not a blank page, not 0 results caused by a system error); there is absolutely NO error popup or technical text (e.g. "AI service unavailable", a stack trace, a 5xx error code) shown on the UI; once the AI Search Service recovers, the system automatically switches back to using AI Search with no manual intervention.</t>
+        </is>
+      </c>
+      <c r="J23" s="27" t="n"/>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="28" t="n"/>
+      <c r="M23" s="28" t="inlineStr">
+        <is>
+          <t>Fills the gap flagged in QnA-32 ("no test case yet exercises the actual Graceful Degradation behavior"). NFR-009 describes this exact behavior almost verbatim, giving a clearer REQ ID anchor — QnA-32 remains open separately for the question of splitting FR-GD-01 from FR-GD-03.</t>
+        </is>
+      </c>
+      <c r="N23" s="27" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>INT-13-SC3</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>Performance &amp; Scalability (NFR)</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>FR-GD-01, NFR-001</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>Measure P95 text-search response time under NORMAL load (as opposed to the peak-load/traffic-spike scenario already tested in INT-13-SC1) — checked against the 300ms P95 threshold per FR-GD-01/NFR-001.</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>AI Search Service, API Gateway, Monitoring</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="inlineStr">
+        <is>
+          <t>The test environment simulates average daily traffic (not peak).</t>
+        </is>
+      </c>
+      <c r="I24" s="27" t="inlineStr">
+        <is>
+          <t>Under average load, P95 text-search response time is &lt;=300ms; this is distinct from the &lt;=1,000ms threshold already tested separately for peak load in INT-13-SC1 (the "peak day" threshold per the BRD KPI-01 note).</t>
+        </is>
+      </c>
+      <c r="J24" s="27" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="28" t="n"/>
+      <c r="M24" s="28" t="n"/>
+      <c r="N24" s="27" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
@@ -14392,7 +20042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="16" min="1" max="2"/>
@@ -16522,6 +22172,222 @@
           <t>This legal risk was already flagged by the BA in the BRD (RSK-05/DEP-08). It is not a new QC finding, but it is repeated here because it directly affects several integration modules (INT-04, INT-11).</t>
         </is>
       </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>INT-13-SC2-TC1</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>INT-13-SC2</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>Performance &amp; Scalability (NFR)</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>FR-GD-03, NFR-009</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>Behavior</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="inlineStr">
+        <is>
+          <t>AI Search down/timeout -&gt; automatic fallback to keyword search, no technical error shown</t>
+        </is>
+      </c>
+      <c r="G32" s="27" t="inlineStr">
+        <is>
+          <t>The test environment can simulate the AI Search Service returning an error/timeout (e.g. disabling the service via a feature flag or blocking network access to the AI endpoint).</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="inlineStr">
+        <is>
+          <t>1. Simulate the AI Search Service timing out/going down.
+2. Perform a normal text search (e.g. "fresh milk").
+3. Check the UI: are any results shown, and does any technical error popup/text appear.
+4. Check whether the returned results come from the basic keyword algorithm (compare against normal AI Search results — e.g. loses synonym/semantic understanding, matches only on raw keywords).
+5. Restore the AI Search Service, repeat the search, confirm the system automatically switches back to using AI Search.</t>
+        </is>
+      </c>
+      <c r="I32" s="27" t="inlineStr">
+        <is>
+          <t>"fresh milk", simulate AI Search down then restore it</t>
+        </is>
+      </c>
+      <c r="J32" s="27" t="inlineStr">
+        <is>
+          <t>Step 3: the customer still gets a results page with products (not blank, no visible error); absolutely no technical popup/toast/text (e.g. "AI service unavailable", a 5xx error code, a stack trace). Step 4: the results reflect basic keyword-search characteristics (possibly less accurate than AI but still reasonable, not empty). Step 5: once AI Search recovers, the system automatically resumes using AI Search with no redeploy or manual ops intervention needed.</t>
+        </is>
+      </c>
+      <c r="K32" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L32" s="28" t="n"/>
+      <c r="M32" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N32" s="28" t="n"/>
+      <c r="O32" s="28" t="n"/>
+      <c r="P32" s="27" t="n"/>
+      <c r="Q32" s="27" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>INT-13-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>INT-13-SC2</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="inlineStr">
+        <is>
+          <t>Performance &amp; Scalability (NFR)</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>FR-GD-03, NFR-009</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F33" s="35" t="inlineStr">
+        <is>
+          <t>Response time while in keyword-search fallback mode — TBD whether the same 300ms SLA applies</t>
+        </is>
+      </c>
+      <c r="G33" s="35" t="inlineStr">
+        <is>
+          <t>The AI Search Service is down/timing out (fallback mode active).</t>
+        </is>
+      </c>
+      <c r="H33" s="35" t="inlineStr">
+        <is>
+          <t>1. While fallback is active, perform searches and measure response time (enough runs to compute P95).
+2. Compare against the 300ms P95 threshold (NFR-001/FR-GD-01) that applies in normal AI Search mode.</t>
+        </is>
+      </c>
+      <c r="I33" s="35" t="inlineStr">
+        <is>
+          <t>Measure P95 response time in fallback mode</t>
+        </is>
+      </c>
+      <c r="J33" s="35" t="inlineStr">
+        <is>
+          <t>TBD — the BRD does not specify whether the performance threshold is relaxed in fallback mode (the keyword algorithm is simpler than AI and could be faster or slower depending on infrastructure) or whether the same 300ms P95 SLA still applies as in normal mode. Cannot be scored against a precise quantitative Pass/Fail until BA/TD confirms the SLA threshold that applies in fallback mode. See QnA-43.</t>
+        </is>
+      </c>
+      <c r="K33" s="35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L33" s="28" t="n"/>
+      <c r="M33" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N33" s="28" t="n"/>
+      <c r="O33" s="28" t="n"/>
+      <c r="P33" s="35" t="inlineStr">
+        <is>
+          <t>QnA-43</t>
+        </is>
+      </c>
+      <c r="Q33" s="35" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-43: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>INT-13-SC3-TC1</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>INT-13-SC3</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>Performance &amp; Scalability (NFR)</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>FR-GD-01, NFR-001</t>
+        </is>
+      </c>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="inlineStr">
+        <is>
+          <t>P95 text-search response time under average load meets the 300ms SLA (FR-GD-01/NFR-001)</t>
+        </is>
+      </c>
+      <c r="G34" s="27" t="inlineStr">
+        <is>
+          <t>The test environment simulates average daily traffic (baseline, not the 5x used in INT-13-SC1).</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="inlineStr">
+        <is>
+          <t>1. Run a load test at average (baseline, 1x) traffic for 15 minutes.
+2. Measure P95 text-search API response time throughout the test.
+3. Compare against the 300ms threshold per NFR-001/FR-GD-01.</t>
+        </is>
+      </c>
+      <c r="I34" s="27" t="inlineStr">
+        <is>
+          <t>Load = 1x average (baseline), 15 minutes</t>
+        </is>
+      </c>
+      <c r="J34" s="27" t="inlineStr">
+        <is>
+          <t>P95 response time is &lt;=300ms — a separate and STRICTER measurement than the &lt;=1,000ms threshold already tested for peak load (5x) in INT-13-SC1-TC1; the two test cases complement each other, covering both normal-load and peak-load conditions against the two distinct thresholds in the BRD (the standard 300ms P95 per NFR-001 vs. the &lt;=1,000ms peak-day note per KPI-01).</t>
+        </is>
+      </c>
+      <c r="K34" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L34" s="28" t="n"/>
+      <c r="M34" s="28" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N34" s="28" t="n"/>
+      <c r="O34" s="28" t="n"/>
+      <c r="P34" s="27" t="n"/>
+      <c r="Q34" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16562,6 +22428,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="17">
       <c r="A3" s="21" t="inlineStr">
         <is>
@@ -16576,7 +22443,7 @@
         </is>
       </c>
       <c r="B4" s="31">
-        <f>COUNTA('UI Test Scenarios'!$B$3:$B$70)+COUNTA('Functional Test Scenarios'!$B$3:$B$22)</f>
+        <f>COUNTA('UI Test Scenarios'!$B$3:$B$85)+COUNTA('Functional Test Scenarios'!$B$3:$B$24)</f>
         <v/>
       </c>
     </row>
@@ -16587,10 +22454,11 @@
         </is>
       </c>
       <c r="B5" s="31">
-        <f>COUNTA('UI Test Cases'!$A$3:$A$114)+COUNTA('Functional Test Cases'!$A$3:$A$31)</f>
+        <f>COUNTA('UI Test Cases'!$A$3:$A$177)+COUNTA('Functional Test Cases'!$A$3:$A$34)</f>
         <v/>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="15" customHeight="1" s="17">
       <c r="A7" s="21" t="inlineStr">
         <is>
@@ -16610,7 +22478,7 @@
         </is>
       </c>
       <c r="B8" s="31">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"Pass")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"Pass")</f>
         <v/>
       </c>
       <c r="D8" s="31" t="inlineStr">
@@ -16619,7 +22487,7 @@
         </is>
       </c>
       <c r="E8" s="31">
-        <f>COUNTIF('Functional Test Cases'!$M$3:$M$31,"Pass")</f>
+        <f>COUNTIF('Functional Test Cases'!$M$3:$M$34,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -16630,7 +22498,7 @@
         </is>
       </c>
       <c r="B9" s="31">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"Fail")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"Fail")</f>
         <v/>
       </c>
       <c r="D9" s="31" t="inlineStr">
@@ -16639,7 +22507,7 @@
         </is>
       </c>
       <c r="E9" s="31">
-        <f>COUNTIF('Functional Test Cases'!$M$3:$M$31,"Fail")</f>
+        <f>COUNTIF('Functional Test Cases'!$M$3:$M$34,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -16650,7 +22518,7 @@
         </is>
       </c>
       <c r="B10" s="31">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"Blocked")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"Blocked")</f>
         <v/>
       </c>
       <c r="D10" s="31" t="inlineStr">
@@ -16659,7 +22527,7 @@
         </is>
       </c>
       <c r="E10" s="31">
-        <f>COUNTIF('Functional Test Cases'!$M$3:$M$31,"Blocked")</f>
+        <f>COUNTIF('Functional Test Cases'!$M$3:$M$34,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -16670,7 +22538,7 @@
         </is>
       </c>
       <c r="B11" s="31">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"N/A")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"N/A")</f>
         <v/>
       </c>
       <c r="D11" s="31" t="inlineStr">
@@ -16679,7 +22547,7 @@
         </is>
       </c>
       <c r="E11" s="31">
-        <f>COUNTIF('Functional Test Cases'!$M$3:$M$31,"N/A")</f>
+        <f>COUNTIF('Functional Test Cases'!$M$3:$M$34,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -16690,7 +22558,7 @@
         </is>
       </c>
       <c r="B12" s="31">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"Not Run")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"Not Run")</f>
         <v/>
       </c>
       <c r="D12" s="31" t="inlineStr">
@@ -16699,7 +22567,7 @@
         </is>
       </c>
       <c r="E12" s="31">
-        <f>COUNTIF('Functional Test Cases'!$M$3:$M$31,"Not Run")</f>
+        <f>COUNTIF('Functional Test Cases'!$M$3:$M$34,"Not Run")</f>
         <v/>
       </c>
     </row>
@@ -16730,7 +22598,7 @@
         </is>
       </c>
       <c r="B14" s="31">
-        <f>COUNTA('UI Test Scenarios'!$B$3:$B$70)</f>
+        <f>COUNTA('UI Test Scenarios'!$B$3:$B$85)</f>
         <v/>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -16739,7 +22607,7 @@
         </is>
       </c>
       <c r="E14" s="31">
-        <f>COUNTA('Functional Test Scenarios'!$B$3:$B$22)</f>
+        <f>COUNTA('Functional Test Scenarios'!$B$3:$B$24)</f>
         <v/>
       </c>
     </row>
@@ -16750,7 +22618,7 @@
         </is>
       </c>
       <c r="B15" s="31">
-        <f>COUNTA('UI Test Cases'!$A$3:$A$114)</f>
+        <f>COUNTA('UI Test Cases'!$A$3:$A$177)</f>
         <v/>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -16759,7 +22627,7 @@
         </is>
       </c>
       <c r="E15" s="31">
-        <f>COUNTA('Functional Test Cases'!$A$3:$A$31)</f>
+        <f>COUNTA('Functional Test Cases'!$A$3:$A$34)</f>
         <v/>
       </c>
     </row>
@@ -16770,7 +22638,7 @@
         </is>
       </c>
       <c r="B16" s="31">
-        <f>COUNTIF('UI Test Cases'!$P$3:$P$114,"QnA*")</f>
+        <f>COUNTIF('UI Test Cases'!$P$3:$P$177,"QnA*")</f>
         <v/>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -16779,10 +22647,11 @@
         </is>
       </c>
       <c r="E16" s="31">
-        <f>COUNTIF('Functional Test Cases'!$P$3:$P$31,"QnA*")</f>
+        <f>COUNTIF('Functional Test Cases'!$P$3:$P$34,"QnA*")</f>
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="17">
       <c r="A18" s="21" t="inlineStr">
         <is>
@@ -16797,7 +22666,7 @@
         </is>
       </c>
       <c r="B19" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"A. Search Bar &amp; Pre-search")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"A. Search Bar &amp; Pre-search")</f>
         <v/>
       </c>
     </row>
@@ -16808,7 +22677,7 @@
         </is>
       </c>
       <c r="B20" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"B. Autocomplete")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"B. Autocomplete")</f>
         <v/>
       </c>
     </row>
@@ -16819,7 +22688,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"C. Auto-Correct Banner")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"C. Auto-Correct Banner")</f>
         <v/>
       </c>
     </row>
@@ -16830,7 +22699,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"D. Search Processing / Loading")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"D. Search Processing / Loading")</f>
         <v/>
       </c>
     </row>
@@ -16841,7 +22710,7 @@
         </is>
       </c>
       <c r="B23" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"E. Search Results — Grid")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"E. Search Results — Grid")</f>
         <v/>
       </c>
     </row>
@@ -16852,7 +22721,7 @@
         </is>
       </c>
       <c r="B24" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"F. Search Results — List")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"F. Search Results — List")</f>
         <v/>
       </c>
     </row>
@@ -16863,7 +22732,7 @@
         </is>
       </c>
       <c r="B25" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"G. Sort")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"G. Sort")</f>
         <v/>
       </c>
     </row>
@@ -16874,7 +22743,7 @@
         </is>
       </c>
       <c r="B26" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"H. Smart Filter / Detailed Filter")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"H. Smart Filter / Detailed Filter")</f>
         <v/>
       </c>
     </row>
@@ -16885,7 +22754,7 @@
         </is>
       </c>
       <c r="B27" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"I. Filter Applied State")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"I. Filter Applied State")</f>
         <v/>
       </c>
     </row>
@@ -16896,7 +22765,7 @@
         </is>
       </c>
       <c r="B28" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"J. Add to Cart")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"J. Add to Cart")</f>
         <v/>
       </c>
     </row>
@@ -16907,7 +22776,7 @@
         </is>
       </c>
       <c r="B29" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"K. Zero-Result Recovery")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"K. Zero-Result Recovery")</f>
         <v/>
       </c>
     </row>
@@ -16918,7 +22787,7 @@
         </is>
       </c>
       <c r="B30" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"L. Image Search — Camera")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"L. Image Search — Camera")</f>
         <v/>
       </c>
     </row>
@@ -16929,7 +22798,7 @@
         </is>
       </c>
       <c r="B31" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"M. Image Search — Gallery")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"M. Image Search — Gallery")</f>
         <v/>
       </c>
     </row>
@@ -16940,7 +22809,7 @@
         </is>
       </c>
       <c r="B32" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"N. Image Search — Recognition Result")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"N. Image Search — Recognition Result")</f>
         <v/>
       </c>
     </row>
@@ -16951,7 +22820,7 @@
         </is>
       </c>
       <c r="B33" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"O. Image Search — Fail")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"O. Image Search — Fail")</f>
         <v/>
       </c>
     </row>
@@ -16962,7 +22831,7 @@
         </is>
       </c>
       <c r="B34" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"P. Voice Search — Listening")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"P. Voice Search — Listening")</f>
         <v/>
       </c>
     </row>
@@ -16973,7 +22842,7 @@
         </is>
       </c>
       <c r="B35" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"Q. Voice Search — Result")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"Q. Voice Search — Result")</f>
         <v/>
       </c>
     </row>
@@ -16984,7 +22853,7 @@
         </is>
       </c>
       <c r="B36" s="31">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"R. Voice Search — Fail")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"R. Voice Search — Fail")</f>
         <v/>
       </c>
     </row>
@@ -16999,6 +22868,7 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="15" customHeight="1" s="17">
       <c r="A39" s="21" t="inlineStr">
         <is>
@@ -17013,7 +22883,7 @@
         </is>
       </c>
       <c r="B40" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Search Ranking Engine")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Search Ranking Engine")</f>
         <v/>
       </c>
     </row>
@@ -17024,7 +22894,7 @@
         </is>
       </c>
       <c r="B41" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Query Understanding — Synonyms &amp; Multilingual")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Query Understanding — Synonyms &amp; Multilingual")</f>
         <v/>
       </c>
     </row>
@@ -17035,7 +22905,7 @@
         </is>
       </c>
       <c r="B42" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Autocomplete &amp; Spelling Correction — Backend")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Autocomplete &amp; Spelling Correction — Backend")</f>
         <v/>
       </c>
     </row>
@@ -17046,7 +22916,7 @@
         </is>
       </c>
       <c r="B43" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Personalization — OMS Integration (Order History)")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Personalization — OMS Integration (Order History)")</f>
         <v/>
       </c>
     </row>
@@ -17057,7 +22927,7 @@
         </is>
       </c>
       <c r="B44" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Sponsored Ads — Retail Media Integration")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Sponsored Ads — Retail Media Integration")</f>
         <v/>
       </c>
     </row>
@@ -17068,7 +22938,7 @@
         </is>
       </c>
       <c r="B45" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Image Search — Computer Vision Service Integration")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Image Search — Computer Vision Service Integration")</f>
         <v/>
       </c>
     </row>
@@ -17079,7 +22949,7 @@
         </is>
       </c>
       <c r="B46" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Voice Search — Speech-to-Text Service Integration")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Voice Search — Speech-to-Text Service Integration")</f>
         <v/>
       </c>
     </row>
@@ -17090,7 +22960,7 @@
         </is>
       </c>
       <c r="B47" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Add to Cart — Cart/OMS Transactional Integration")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Add to Cart — Cart/OMS Transactional Integration")</f>
         <v/>
       </c>
     </row>
@@ -17101,7 +22971,7 @@
         </is>
       </c>
       <c r="B48" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Catalog &amp; Inventory — Real-Time Stock Sync")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Catalog &amp; Inventory — Real-Time Stock Sync")</f>
         <v/>
       </c>
     </row>
@@ -17112,7 +22982,7 @@
         </is>
       </c>
       <c r="B49" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Zero-Result Fallback Engine — Recommendation Algorithm")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Zero-Result Fallback Engine — Recommendation Algorithm")</f>
         <v/>
       </c>
     </row>
@@ -17123,7 +22993,7 @@
         </is>
       </c>
       <c r="B50" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Auth &amp; Session — Guest vs Member")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Auth &amp; Session — Guest vs Member")</f>
         <v/>
       </c>
     </row>
@@ -17134,7 +23004,7 @@
         </is>
       </c>
       <c r="B51" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Analytics &amp; Event Logging")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Analytics &amp; Event Logging")</f>
         <v/>
       </c>
     </row>
@@ -17145,7 +23015,7 @@
         </is>
       </c>
       <c r="B52" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Performance &amp; Scalability (NFR)")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Performance &amp; Scalability (NFR)")</f>
         <v/>
       </c>
     </row>
@@ -17156,7 +23026,7 @@
         </is>
       </c>
       <c r="B53" s="31">
-        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$22,"Security &amp; Data Privacy (PDPL)")</f>
+        <f>COUNTIF('Functional Test Scenarios'!$C$3:$C$24,"Security &amp; Data Privacy (PDPL)")</f>
         <v/>
       </c>
     </row>
@@ -17171,6 +23041,7 @@
         <v/>
       </c>
     </row>
+    <row r="55"/>
     <row r="56" ht="15" customHeight="1" s="17">
       <c r="A56" s="21" t="inlineStr">
         <is>
@@ -17185,7 +23056,7 @@
         </is>
       </c>
       <c r="B57" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Normal")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Normal")</f>
         <v/>
       </c>
     </row>
@@ -17196,7 +23067,7 @@
         </is>
       </c>
       <c r="B58" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Functional")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Functional")</f>
         <v/>
       </c>
     </row>
@@ -17207,7 +23078,7 @@
         </is>
       </c>
       <c r="B59" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Validation")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Validation")</f>
         <v/>
       </c>
     </row>
@@ -17218,7 +23089,7 @@
         </is>
       </c>
       <c r="B60" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Negative")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Negative")</f>
         <v/>
       </c>
     </row>
@@ -17229,7 +23100,7 @@
         </is>
       </c>
       <c r="B61" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Boundary")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Boundary")</f>
         <v/>
       </c>
     </row>
@@ -17240,7 +23111,7 @@
         </is>
       </c>
       <c r="B62" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Edge")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Edge")</f>
         <v/>
       </c>
     </row>
@@ -17251,7 +23122,7 @@
         </is>
       </c>
       <c r="B63" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Exception")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Exception")</f>
         <v/>
       </c>
     </row>
@@ -17262,7 +23133,7 @@
         </is>
       </c>
       <c r="B64" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Integration")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Integration")</f>
         <v/>
       </c>
     </row>
@@ -17273,7 +23144,7 @@
         </is>
       </c>
       <c r="B65" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Performance")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Performance")</f>
         <v/>
       </c>
     </row>
@@ -17284,7 +23155,7 @@
         </is>
       </c>
       <c r="B66" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Sponsored")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Sponsored")</f>
         <v/>
       </c>
     </row>
@@ -17295,7 +23166,7 @@
         </is>
       </c>
       <c r="B67" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Ranking")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Ranking")</f>
         <v/>
       </c>
     </row>
@@ -17306,7 +23177,7 @@
         </is>
       </c>
       <c r="B68" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"No-result")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"No-result")</f>
         <v/>
       </c>
     </row>
@@ -17317,7 +23188,7 @@
         </is>
       </c>
       <c r="B69" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Typo")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Typo")</f>
         <v/>
       </c>
     </row>
@@ -17328,7 +23199,7 @@
         </is>
       </c>
       <c r="B70" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Sort")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Sort")</f>
         <v/>
       </c>
     </row>
@@ -17339,7 +23210,7 @@
         </is>
       </c>
       <c r="B71" s="31">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Filter")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Filter")</f>
         <v/>
       </c>
     </row>
@@ -17354,6 +23225,7 @@
         <v/>
       </c>
     </row>
+    <row r="73"/>
     <row r="74" ht="15" customHeight="1" s="17">
       <c r="A74" s="21" t="inlineStr">
         <is>
@@ -17368,7 +23240,7 @@
         </is>
       </c>
       <c r="B75" s="31">
-        <f>COUNTIF('Functional Test Cases'!$E$3:$E$31,"Functional")</f>
+        <f>COUNTIF('Functional Test Cases'!$E$3:$E$34,"Functional")</f>
         <v/>
       </c>
     </row>
@@ -17379,7 +23251,7 @@
         </is>
       </c>
       <c r="B76" s="31">
-        <f>COUNTIF('Functional Test Cases'!$E$3:$E$31,"Behavior")</f>
+        <f>COUNTIF('Functional Test Cases'!$E$3:$E$34,"Behavior")</f>
         <v/>
       </c>
     </row>
@@ -17390,7 +23262,7 @@
         </is>
       </c>
       <c r="B77" s="31">
-        <f>COUNTIF('Functional Test Cases'!$E$3:$E$31,"Integration")</f>
+        <f>COUNTIF('Functional Test Cases'!$E$3:$E$34,"Integration")</f>
         <v/>
       </c>
     </row>
@@ -17401,7 +23273,7 @@
         </is>
       </c>
       <c r="B78" s="31">
-        <f>COUNTIF('Functional Test Cases'!$E$3:$E$31,"Boundary")</f>
+        <f>COUNTIF('Functional Test Cases'!$E$3:$E$34,"Boundary")</f>
         <v/>
       </c>
     </row>
@@ -17412,7 +23284,7 @@
         </is>
       </c>
       <c r="B79" s="31">
-        <f>COUNTIF('Functional Test Cases'!$E$3:$E$31,"Negative")</f>
+        <f>COUNTIF('Functional Test Cases'!$E$3:$E$34,"Negative")</f>
         <v/>
       </c>
     </row>
@@ -17423,7 +23295,7 @@
         </is>
       </c>
       <c r="B80" s="31">
-        <f>COUNTIF('Functional Test Cases'!$E$3:$E$31,"Performance")</f>
+        <f>COUNTIF('Functional Test Cases'!$E$3:$E$34,"Performance")</f>
         <v/>
       </c>
     </row>
@@ -17434,7 +23306,7 @@
         </is>
       </c>
       <c r="B81" s="31">
-        <f>COUNTIF('Functional Test Cases'!$E$3:$E$31,"Security")</f>
+        <f>COUNTIF('Functional Test Cases'!$E$3:$E$34,"Security")</f>
         <v/>
       </c>
     </row>
